--- a/Con_Law_Case_Chart.xlsx
+++ b/Con_Law_Case_Chart.xlsx
@@ -3832,7 +3832,8 @@
           <t>• Necessary and Proper failed because the mandate is not "proper": it lets Congress create the predicate for exercising its own power; Raich distinguished
 • Roberts reached the commerce question only because the tax reading was a saving construction needed if the command failed; fn. 3: Ginsburg's other mandates (jury duty, draft) rest on powers other than commerce
 • Ginsburg: joins the tax holding, but would also uphold the mandate under the Commerce Clause (unique health market, free riders, the "broccoli horrible" piles inference upon inference) and the Medicaid expansion as enacted
-• Joint dissent: self-insurance is "wordplay"; "If all inactivity affecting commerce is commerce, commerce is everything"; would hold the whole Act inoperative</t>
+• Joint dissent: self-insurance is "wordplay"; "If all inactivity affecting commerce is commerce, commerce is everything"; would hold the whole Act inoperative
+• Medicaid "shift in kind, not merely degree": original program covered four categories of the needy; expansion covers the entire nonelderly population below 133% of poverty; separate funding provision (90% for newly eligible vs. 50-83%); less comprehensive coverage. Congress had styled it a mere alteration of existing Medicaid; Roberts looked past the label</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">

--- a/Con_Law_Case_Chart.xlsx
+++ b/Con_Law_Case_Chart.xlsx
@@ -11,7 +11,7 @@
     <sheet name="How to use" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Case Chart'!$A$1:$I$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Case Chart'!$A$1:$I$113</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -44,7 +44,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -59,6 +59,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EEF2F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6F1E4"/>
       </patternFill>
     </fill>
   </fills>
@@ -79,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -94,6 +99,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -462,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I94"/>
+  <dimension ref="A1:I113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1325,40 +1336,273 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Course reader timeline</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Background dates</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>A one-page chronology from the Articles (1781) through recent cases.</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Places the readings in order.</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Use for sequence, not memorization: Articles (1781) → Convention (1787) → government begins and Judiciary Act (1789) → Bank and Bill of Rights (1791) → Marbury (1803) → McCulloch (1819) → Gibbons (1824) → Reconstruction Amendments (1865-1870) → 1937 switch → Wickard (1942) → Lopez (1995).</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>• Know the order of events where it matters to an argument (e.g., Chisholm 1793 before the Eleventh Amendment; McCulloch before Gibbons)
+• Dates alone are rarely tested</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Helps frame 'then vs. now' answers (Federalist 45 then; Wickard/Raich now).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Declaration of Independence (1776)</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Founding principles</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Statement of grievances and principles justifying independence.</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Governments derive "their just powers from the consent of the governed."</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Popular sovereignty and the right to "alter or to abolish" a government destructive of its ends.</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>• Consent of the governed is the key phrase
+• Unalienable rights: "Life, Liberty and the pursuit of Happiness"</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>Use for popular-sovereignty arguments (e.g., Wilson and Jay in Chisholm; Marshall in McCulloch that the government "proceeds directly from the people").</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Articles of Confederation (1781)</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Founding structure</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>The first national charter: a league of sovereign states with a weak Congress.</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Each state keeps its sovereignty and every power not "expressly delegated" (Art. II).</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>A "firm league of friendship"; one vote per state; Congress could not tax (states raised money); major acts needed nine states; amendment required unanimity.</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>• "Expressly delegated" in Art. II is the word the Tenth Amendment OMITS (McCulloch's point)
+• No federal taxing power and legislation for states, not individuals, is Federalist 15's "radical vice"
+• Unanimity for amendments</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>Background for why the Constitution was needed (Federalist 15) and for McCulloch's reading of the Tenth Amendment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Martineau, Society in America (1837)</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Critique of judicial tenure</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>An English observer's view of American institutions.</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Life-tenured judges hold a "virtually irresponsible office," an inconsistency in a republic.</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>The judiciary is "not republican at all"; the House is mainly republican, the Senate only partly.</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>• Her critique is about accountability of life tenure
+• Pairs with Brutus 15 (judges independent of the people)</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>Counterpoint to Federalist 78's defense of life tenure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>CRS, Modes of Constitutional Interpretation (R45129)</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Interpretation methods</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>A CRS report describing how courts interpret the Constitution.</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Lists eight modes of interpretation.</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Textualism; original meaning; judicial precedent (the most commonly cited); pragmatism; moral reasoning; national identity ("ethos"); structuralism; historical practices.</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>• Textualism looks to the text's plain meaning; original meaning looks to how the public understood it at the Founding
+• Precedent is "the most commonly cited source"
+• Structuralism draws inferences from separation of powers and federalism (e.g., McCulloch, Alden)
+• Historical practices matter most when the text is unclear</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>Name the mode an opinion uses (e.g., Thomas in Lopez: original meaning; Kennedy in Lopez: precedent; Alden and Torres: structure and history).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Massachusetts v. Mellon / Frothingham v. Mellon (1923)</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Standing: taxpayer and state</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Massachusetts (original suit) and a federal taxpayer challenged the Maternity Act, which gave grants to states that accepted it.</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Both suits were dismissed for want of jurisdiction without reaching the merits.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>A party must show a "direct injury" from the statute, "not merely that he suffers in some indefinite way in common with people generally." A state's bare claim that Congress usurped reserved powers is political, not judicial.</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>• State: the Act imposed no obligation, just an option it could reject "by the simple expedient of not yielding"
 • Federal taxpayer's interest is "minute and indeterminable" and the tax effect "remote, fluctuating and uncertain"; a municipal taxpayer's is direct, like a stockholder's
@@ -1366,47 +1610,47 @@
 • Hearing it would assume authority over a co-equal department</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>Starting point for the taxpayer-standing line (Flast, Richardson, Hein) and the generalized-grievance bar.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
+    <row r="25">
+      <c r="A25" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Flast v. Cohen (1968)</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Standing: taxpayer (Establishment)</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Seven federal taxpayers challenged federal education funds used for instruction and textbooks in religious schools under the Establishment and Free Exercise Clauses.</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Taxpayers have standing to challenge congressional taxing-and-spending action that violates a specific constitutional limit on that power; reversed.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Two-part nexus test: (1) the challenge targets an exercise of Congress's Art. I, Sec. 8 taxing and spending power, not incidental spending under a regulatory statute; (2) the enactment exceeds a specific constitutional limitation on that power, such as the Establishment Clause.</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>• Frothingham met the first nexus but failed the second (general Art. I / Tenth Amendment claim)
 • "Iceberg quality" of "cases" and "controversies": adversary context plus separation of powers = justiciability
@@ -1414,47 +1658,47 @@
 • Douglas: test not durable, overrule Frothingham now; Harlan dissented</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>The high-water mark of taxpayer standing, later confined to its facts (Richardson, Hein); Powell and Scalia urged abandoning or overruling it.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
+    <row r="26">
+      <c r="A26" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Sierra Club v. Morton (1972)</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Standing: aesthetic injury</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>The Sierra Club sued under the APA to stop a Disney ski resort in Mineral King valley, alleging only its special interest in conservation.</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>No standing: the Club did not allege that it or its members used Mineral King; affirmed.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Aesthetic and environmental harm can be injury in fact, but the plaintiff must "be himself among the injured." A mere "interest in a problem" is not enough.</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>• Widely shared interests are not less deserving of protection
 • Court noted the Club could amend under Rule 15 (members who use the area would likely have standing)
@@ -1462,47 +1706,47 @@
 • Blackmun dissent: approve on condition of amendment, or an "imaginative expansion" of standing</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>Key for injury-in-fact and organizational standing; leads to Lujan's use-the-area requirement and Douglas v. NPS.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
+    <row r="27">
+      <c r="A27" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>United States v. Richardson (1974)</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Standing: generalized grievance</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>A taxpayer and voter challenged secret CIA expenditures under the Statement and Account Clause, claiming he could not follow government or vote intelligently.</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>No standing; reversed. His claim fails the Flast test and is a generalized grievance "common to all members of the public."</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Undifferentiated harms shared by all citizens belong to Congress and the political process, not the courts.</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>• No "Athenian democracy or New England town meeting" by lawsuit
 • Powell concurring: abandon the Flast nexus test but keep Flast on its facts
@@ -1510,94 +1754,94 @@
 • Halperin v. CIA (D.C. Cir.): FOIA plaintiff also lacked standing under the Clause</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>Leading generalized-grievance case; FEC v. Akins distinguishes it where a statute grants the information right.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
+    <row r="28">
+      <c r="A28" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>City of Los Angeles v. Lyons (1983)</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Standing: injunctions, future harm</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>LA police choked Lyons unconscious during a traffic stop; he sought damages and an injunction against chokeholds.</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Lyons lacked standing to seek the injunction because he showed no "real and immediate threat" of being choked again.</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Past injury may support damages but not prospective relief; standing must be shown for each form of relief.</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>• "Incredible assertion" needed: another police encounter AND either all officers always choke or the City ordered it
 • Without likely future injury he is no more entitled to an injunction than any other citizen
 • Marshall dissent: majority fragments standing by remedy; standing turns on the stake in the dispute</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>Use for injunctive-relief standing and imminence; TransUnion and Clapper build on it.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
+    <row r="29">
+      <c r="A29" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>Allen v. Wright (1984)</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Standing: framework</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>The excerpt gives no facts; it is read for O'Connor's statement of standing doctrine.</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>The excerpt states the framework, not a disposition: Art. III standing is built on separation of powers.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>Constitutional core: personal injury fairly traceable to the defendant's conduct and likely redressed by the relief. Prudential limits: no third-party rights, no generalized grievances, zone of interests.</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>• Three questions: injury too abstract? causation too attenuated? relief too speculative?
 • Injury must be "distinct and palpable," not abstract, conjectural or hypothetical
@@ -1605,47 +1849,47 @@
 • Quotes Bork (Vander Jagt): doctrines rest on an idea "more than an intuition but less than a rigorous and explicit theory"</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>Cite for the three-element test and the separation-of-powers basis of standing; Davis's complexity critique is the counterpoint.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
+    <row r="30">
+      <c r="A30" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>Lujan v. Defenders of Wildlife (1992)</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Standing: elements; procedural</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Wildlife groups challenged an Interior rule limiting ESA consultation to actions in the U.S. or high seas; members had visited foreign habitats and hoped to return some day.</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>No standing; reversed and remanded.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>"Irreducible constitutional minimum": (1) injury in fact, concrete and particularized and actual or imminent; (2) causation, fairly traceable to the defendant; (3) redressability, likely not speculative. Congress cannot convert the public interest in lawful government into an individual right.</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>• "Some day" intentions without concrete plans are not imminent
 • Rejected ecosystem, animal and vocational nexus theories (Bronx Zoo keeper "beyond all reason")
@@ -1653,47 +1897,47 @@
 • Procedural right needs a concrete interest; fn. 7 relaxes redressability for a dam neighbor; Kennedy concurred, Blackmun dissented ("slash-and-burn")</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>Central standing test; links to Take Care Clause separation-of-powers theme. Akins and TransUnion test how far Congress can create standing.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
+    <row r="31">
+      <c r="A31" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>FEC v. Akins (1998)</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Standing: informational injury</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Voters challenged the FEC's ruling that AIPAC was not a "political committee" required to disclose donors and spending.</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>The voters had standing; remanded.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>Failure to obtain information a statute requires to be public is injury in fact; a widely shared but concrete injury is not a barred generalized grievance.</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>• Distinguished Richardson: a statute protects these plaintiffs, and Richardson was about taxpayer standing
 • Injury "directly related to voting, the most basic of political rights"
@@ -1701,93 +1945,184 @@
 • Scalia dissent: Richardson reduced to a "curio"; "burnt leg, burnt arm"; transfers the Take Care duty to courts</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>Shows Congress can create standing through statutory information rights; contrast Lujan and TransUnion.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="n">
+    <row r="32">
+      <c r="A32" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Justices' letter to Washington (Aug. 8, 1793)</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>Advisory opinions: refusal</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>The Justices' reply to Jefferson's July 18 request for advice.</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>The Justices declined to decide the questions "extrajudicially."</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>Separation of powers bars federal judges from giving advisory opinions outside a case.</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>• Three reasons: lines of separation among the departments; departments as checks on each other; Justices are judges of a court in the last resort
 • Textual point: the President's power to call for opinions is limited to executive department heads</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="I32" s="4" t="inlineStr">
         <is>
           <t>Root of the no-advisory-opinions rule; connect to standing cases that describe what courts do not do (TransUnion, Sierra Club fn. 3).</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
+    <row r="33">
+      <c r="A33" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Moore's Federal Practice: standing sections</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Standing treatise</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>Assigned treatise sections giving an overview of standing.</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>Standing focuses on WHO may bring suit (§ 101.20).</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>Standing has constitutional and prudential components (§ 101.22); only one plaintiff needs standing (§ 101.23).</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>• "Only one plaintiff need have standing"
+• Assigned partly to teach how to use a treatise</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>Cite for the one-plaintiff rule when multiple plaintiffs sue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Davis, Administrative Law Treatise (1983)</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Critique of standing law</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>A treatise author's assessment of standing doctrine.</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>Standing law's "main failure" is "the inconsistency, unreliability, and inordinate complexity," not that courts open the doors too much or too little.</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>Professor adds Thole v. U.S. Bank (2020): "Courts sometimes make standing law more complicated than it needs to be." ("Any court in particular?")</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>• The criticism is inconsistency and complexity, not too much or too little access</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>Use as a critique in a standing essay (with Douglas in Flast and Powell in Richardson).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>Hein v. Freedom from Religion Found. (2007)</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Standing: taxpayer (Executive)</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Taxpayers challenged White House faith-based conferences funded from general Executive Branch appropriations under the Establishment Clause.</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>No taxpayer standing; reversed. Flast does not reach discretionary Executive Branch expenditures.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>The Flast exception is narrow, covers only congressional laws authorizing spending, and has largely been confined to its facts.</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>• Plurality (Alito), not a majority opinion
 • Scalia (with Thomas): overrule Flast; Alito: Scalia is "wrong," "We decide only the case at hand"
@@ -1795,47 +2130,47 @@
 • Other clauses never supported taxpayer standing (Richardson, Valley Forge, Cuno)</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>End of the taxpayer-standing line from Frothingham through Flast and Richardson; shows narrowing without overruling.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
+    <row r="36">
+      <c r="A36" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>Clapper v. Amnesty Int'l USA (2013)</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Standing: certainly impending</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Lawyers and organizations who communicate with people abroad challenged FISA Sec. 702 the day it passed, fearing interception and paying to avoid it.</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>No standing; reversed. The feared injury was not certainly impending or fairly traceable, and plaintiffs cannot manufacture standing by spending money.</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Threatened injury must be "certainly impending"; possible future injury is not enough. Standing review is especially rigorous where the merits would strike down another branch's action.</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>• Five-link "highly attenuated chain"; link 2 (use of 1881a vs. other authority) defeats traceability
 • FISC approval made injury depend on independent judges
@@ -1843,94 +2178,94 @@
 • Breyer dissent: certainty is not the touchstone; "certainly" is emphasis</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>Leading imminence case; SBA List softens it with "substantial risk," and Douglas applies it to aesthetic injury.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
+    <row r="37">
+      <c r="A37" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>Susan B. Anthony List v. Driehaus (2014)</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Standing: pre-enforcement</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>The excerpt gives no facts; it addresses standing for a pre-enforcement challenge.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Petitioners showed injury in fact; reversed and remanded for the remaining standing elements.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>Pre-enforcement injury exists where the plaintiff intends conduct arguably affected with a constitutional interest, proscribed by statute, with a credible threat of prosecution (Babbitt). Future injury suffices if "certainly impending" or a "substantial risk."</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>• No need to be arrested or prosecuted first (Steffel)
 • Credible threat: past enforcement against others and refusal to disavow (Holder); well-founded fear plus costly compliance (American Booksellers)
 • Fn. 5: standing and ripeness boil down to the same question</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>Use for pre-enforcement challenges; bridges standing (Clapper) and ripeness (Texas v. United States).</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
+    <row r="38">
+      <c r="A38" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>TransUnion LLC v. Ramirez (2021)</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Standing: concrete harm</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>A class of 8,185 sued under FCRA over false OFAC "potential terrorist" alerts; only 1,853 had reports sent to businesses, and mailing-format claims were added.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Only the 1,853 had standing on the reasonable-procedures claim; only Ramirez had standing on the two mailing claims; reversed and remanded.</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>"No concrete harm, no standing": a harm is concrete if it bears a close relationship to a harm traditionally recognized in American courts. An injury in law is not an injury in fact, and every class member needs standing for damages.</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>• Dissemination is like defamation; undisclosed file is a letter in a desk drawer
 • Risk of future harm can support an injunction but not damages alone (reckless-driver example)
@@ -1938,94 +2273,94 @@
 • Thomas dissent: private rights need no actual damage, "pyrrhic victory" sends suits to state court; Kagan: "judicial aggrandizement"</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>Limits Congress's power to create standing (contrast Akins); ties to separation of powers and to Lyons's relief-by-relief analysis.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
+    <row r="39">
+      <c r="A39" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>SFFA v. Harvard (2023) (standing)</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Standing: organizational</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>SFFA, a membership nonprofit, sued Harvard and UNC over race-based admissions; UNC said SFFA was not a genuine membership organization.</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>SFFA had organizational standing; UNC's standing objection was rejected.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>Hunt test for representational standing: members would have standing; interests germane to the organization's purpose; no need for individual members' participation.</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>• Hunt's "indicia of membership" applies to memberless entities, not voluntary groups with identified members
 • Identified members represented in good faith need no further scrutiny of how the group operates
 • 47 members at filing; four rejected applicants filed declarations</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t>Use for associational standing; contrast Sierra Club, where the group failed to allege members' injury.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
+    <row r="40">
+      <c r="A40" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>Douglas v. National Park Service (D.D.C. 2026)</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Standing: aesthetic, procedural</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Two plaintiffs sought a TRO against a UFC event on the White House South Lawn and Lincoln Memorial, alleging aesthetic, dignitary, physical and NEPA injuries.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>TRO denied: plaintiffs showed neither a substantial likelihood of standing nor irreparable harm.</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>Aesthetic injury requires concrete plans to be directly affected and must be certainly impending (Clapper); a procedural right "in vacuo" is not enough.</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>• Romano: only a "serendipitous rideshare trip" would bring him there
 • Douglas came to protest, not for aesthetics; general emotional harm is not enough
@@ -2033,235 +2368,373 @@
 • Plaintiffs must show a "substantial likelihood" of standing for a TRO</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>Applies Sierra Club, Lujan and Clapper to current facts; good model for an aesthetic-injury hypo.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
+    <row r="41">
+      <c r="A41" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>Texas v. United States (1998)</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Ripeness</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Texas sought a declaration that Voting Rights Act preclearance did not apply to state sanctions (appointing a master or management team) for failing school districts.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Not ripe; the Court agreed with the three-judge District Court.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>A claim resting on "contingent future events that may not occur as anticipated, or indeed may not occur at all" is unripe. Abbott Labs test: fitness of the issues and hardship of withholding review.</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>• Not fit: no district identified, better decided in a particular application, no state-court interpretation
 • No hardship: Texas need not do or refrain from anything; it can just go ahead and appoint
 • "Threat to federalism" is an abstraction; contrast Abbott Labs' direct day-to-day effect</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr">
         <is>
           <t>Core ripeness case; pair with SBA List fn. 5 on the overlap of ripeness and standing.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
+    <row r="42">
+      <c r="A42" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>Roe v. Wade (1973) (mootness)</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Mootness: capable of repetition</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Roe, pregnant when she sued in 1970, was no longer shown pregnant by the time of judgment and appeal.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Not moot: pregnancy is "capable of repetition, yet evading review."</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>An actual controversy must exist at every stage of review, but an exception applies to short, recurring injuries.</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>• 266-day gestation is shorter than appellate review; pregnancy can recur
 • "Our law should not be that rigid"
 • Merits (abortion right) are not part of Con Law I</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>Classic capable-of-repetition example; Klaassen shows the exception's limits.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
+    <row r="43">
+      <c r="A43" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>City of Mesquite v. Aladdin's Castle (1981)</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Mootness: voluntary cessation</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>While the case was on appeal, Mesquite deleted the challenged "connections with criminal elements" licensing language; it had earlier reenacted an age rule after losing.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Not moot; the Court reached the vagueness merits.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>Voluntary cessation does not deprive a court of power to decide; a case is moot only if it is "absolutely clear" the conduct could not reasonably be expected to recur.</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>• City could reenact if the judgment were vacated and said so at oral argument
 • Test is "stringent"; otherwise defendants would be "free to return to his old ways"
 • If a case becomes moot on appeal, the judgment below is normally vacated</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr">
         <is>
           <t>Leading voluntary-cessation case; use whenever a government repeals a challenged rule during litigation.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
+    <row r="44">
+      <c r="A44" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>Klaassen v. Trustees of Indiana Univ. (7th Cir. 2022)</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Mootness: limits of exception</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Students challenged Indiana University's COVID-19 vaccine requirement; the only plaintiff without a religious exemption withdrew with no plans to return.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Moot; judgment vacated and remanded with instructions to dismiss.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Capable-of-repetition-yet-evading-review applies only if the dispute can recur between the same parties and is too short-lived for review.</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>• Two reasons the exception failed: no recurrence for these plaintiffs; policy not evanescent (four-year enrollment)
 • Abandoned mask-and-test claim could not be revived post-argument
 • "The only plaintiff with standing withdrew from the University"</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>Contrast with Roe: the exception needs both a short duration and recurrence for the same plaintiff.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
+    <row r="45">
+      <c r="A45" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>FISC website: About the Foreign Intelligence Surveillance Court</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Background for Clapper</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>The court's own description of itself.</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>"The FISC is an Article III federal court."</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>Created by FISA (1978) to review government applications for foreign-intelligence surveillance; 11 district judges designated by the Chief Justice for up to seven years, from at least seven circuits, three living near D.C.</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>• It is an Article III court
+• Its judges are designated by the Chief Justice</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>Background for Clapper: the FISC's secret approval process is part of why the plaintiffs could only speculate about surveillance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>TransUnion v. Ramirez: oral argument (2021)</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>Standing: concreteness</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>Transcript of the Supreme Court argument.</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>Previews the concreteness debate the Court decided.</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>Issacharoff (for Ramirez): an OFAC label is "the scarlet letter of our time"; closest common-law analogue is defamation per se. Clement (TransUnion) pressed the "desk drawer" point that undisclosed files harm no one.</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>• Alito asked for the closest common-law analogue to suing over an unknown past risk
+• His 1786 hypothetical: an unpublished defamatory article can't support suit, like files never disseminated</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>Shows why dissemination became the dividing line in the decision (1,853 vs. 6,332).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>Moore's Federal Practice: ripeness sections</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>Ripeness treatise</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>Assigned sections on the nature of ripeness, its relation to standing, and its criteria.</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>"Fitness" and "hardship" are the primary criteria (§ 101.76).</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>Ripeness and standing overlap (§ 101.71); see Texas v. United States for the application.</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>• Fitness and hardship are the two criteria
+• Ripeness and standing often "boil down to the same question" (SBA List fn. 5)</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>Pair with Texas v. United States and Abbott Labs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>Chisholm v. Georgia (1793)</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>State sovereign immunity</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>A South Carolina citizen sued Georgia in assumpsit to collect a debt, invoking the Supreme Court's original jurisdiction. Georgia refused to appear and filed a remonstrance.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>A State could be sued in federal court by a citizen of another State; Justice Iredell alone dissented.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>The majority read Article III's literal grant over controversies 'between a State and Citizens of another State' to defeat state immunity. The Eleventh Amendment overruled the result, and Hans and Alden treat Iredell's dissent as the original understanding.</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>• The case began in the Supreme Court under its original jurisdiction, not on appeal
 • Four majority Justices wrote separately on the literal text: Wilson and Jay said immunity clashed with popular sovereignty; Blair and Cushing found a surrender in Art. III
@@ -2269,47 +2742,47 @@
 • Alden: the 'shall not be construed to extend' wording shows Congress overruled Chisholm rather than changed Article III; VOPA: the Amendment's text 'only eliminates the basis for our judgment' in Chisholm</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr">
         <is>
           <t>Open any sovereign immunity answer here: text (Chisholm majority) versus structure and history (Iredell, Hans, Alden). Counterpoint: the swift amendment may mean the country 'changed its collective mind' rather than restored an original understanding (Currie, quoted in Alden).</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
+    <row r="49">
+      <c r="A49" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>Hans v. Louisiana (1890)</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>State sovereign immunity</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>A Louisiana citizen sued Louisiana in federal court, claiming a state constitutional amendment impaired the obligation of contracts, so the case arose under federal law.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>A State cannot be sued in federal court by its own citizen without its consent, even in a federal-question case and even though the Eleventh Amendment's text covers only out-of-state and foreign plaintiffs.</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>State immunity is not confined to the Eleventh Amendment's text; the Amendment reflects a broader principle that a sovereign is not suable by individuals without consent. A State may waive immunity and set the terms of its consent.</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>• Rejected the 'anomalous result' that a State could be sued by its own citizens but not by citizens of other States
 • The Amendment 'actually reversed' Chisholm and vindicated Iredell's 'able opinion' over the majority's reliance on the 'letter'
@@ -2317,47 +2790,47 @@
 • Proviso hypothetical: an amendment expressly allowing own-citizen suits would never have been ratified ('almost an absurdity')</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr">
         <is>
           <t>Hans starts the structural immunity line (Hans, Alden, Allen, VOPA): immunity comes from history and the plan of the Constitution, not the Amendment's words. Counterpoint: a textualist reading like the Chisholm majority's.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
+    <row r="50">
+      <c r="A50" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>Ex parte Young (1908)</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Sovereign immunity: officer suits</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Railroad shareholders won a federal injunction barring Minnesota's Attorney General, Edward Young, from enforcing allegedly confiscatory rate laws backed by huge penalties. Young sued in state court to enforce the rates anyway, was held in contempt, and sought habeas in the Supreme Court.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>The federal court had jurisdiction to enjoin the Attorney General from enforcing an unconstitutional state law; the penalty provisions were unconstitutional on their face.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>An officer who enforces an unconstitutional state act is 'stripped of his official or representative character,' so a suit to enjoin him is not a suit against the State. The officer must have some connection with enforcing the act; a general duty to enforce state law is enough.</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>• The injunction runs against the officer only: a federal court may NOT enjoin a state court or a grand jury
 • Disobey-and-defend was inadequate: few agents would risk heavy fines and prison to test the law, and rate questions are too complex for a jury
@@ -2365,47 +2838,47 @@
 • Edelman called Young a 'watershed' that let the Civil War Amendments serve 'as a sword'; CRS and VOPA call it a 'fiction'</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr">
         <is>
           <t>Young is the main exception to immunity: prospective relief against officers for ongoing violations of federal law. Pair it with its limits (Edelman: no retroactive money; CRS: no state-law claims) and its extension in VOPA.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
+    <row r="51">
+      <c r="A51" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>Edelman v. Jordan (1974)</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Sovereign immunity: remedies</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>A class sued Illinois public aid officials in federal court for processing disability benefit applications late, in violation of federal time limits. The district court ordered prospective compliance and payment of benefits wrongfully withheld in the past.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>The Eleventh Amendment bars the retroactive award of benefits paid from the state treasury; prospective injunctive relief under Ex parte Young is allowed.</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>When a suit is in essence for money from the state treasury, the State is the real party in interest even if officials are named. An 'ancillary effect on the state treasury' that comes from complying with a prospective decree is permissible.</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>• Line drawn between future compliance and 'reparation for the past' (Judge McGowan in Rothstein v. Wyman); the line is not always 'between day and night'
 • No 'constructive consent': joining a federal program is not waiver; waiver needs 'the most express language' or overwhelming implication
@@ -2413,47 +2886,47 @@
 • Disapproved Shapiro v. Thompson and summary affirmances to the extent inconsistent; stare decisis is weaker on constitutional questions</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr">
         <is>
           <t>Use Edelman to limit Ex parte Young: prospective relief yes, retroactive money no. It also supplies the strict waiver standard later used in the CRS report and Alden.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
+    <row r="52">
+      <c r="A52" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>Alden v. Maine (1999)</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>State sovereign immunity</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Maine probation officers sued the State for FLSA overtime. After Seminole Tribe ended their federal suit, they refiled in Maine's own courts, which dismissed on sovereign immunity.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Congress's Article I powers do not include power to subject nonconsenting States to private damages suits in their own courts, and Maine had not consented.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>State immunity is a fundamental aspect of sovereignty retained at ratification, except as altered by the plan of the Convention or certain amendments; the Eleventh Amendment 'confirmed rather than established' it. It does not bar consented suits, suits by the United States or other States, valid Section 5 abrogation, suits against municipalities, Ex parte Young injunctions against officers, or individual-capacity damages against officers.</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>• 'Eleventh Amendment immunity' is 'something of a misnomer': immunity comes from structure, so it reaches state courts even though the text limits only 'the Judicial power of the United States'
 • Suits by the United States differ because they require 'political responsibility' for each suit; here the U.S. did not send 'even a single attorney to Maine'
@@ -2461,47 +2934,47 @@
 • Souter dissent: the immunity rests on bad history and resembles Lochner-era doctrine, 'probably as fleeting'; Torres later narrowed Alden's Article I statement</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr">
         <is>
           <t>Alden is the high-water mark of the dignity rationale: 'Congress has vast power but not all power.' Use its list of remaining avenues (U.S. suits, Young, officer damages) for hypos; counterpoint is Torres, which lets Article I war powers override immunity in state court.</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
+    <row r="53">
+      <c r="A53" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>Baker v. Carr (1962)</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Political question doctrine</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>The reader excerpt omits the facts and gives only Justice Brennan's statement of the political question doctrine.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>A case should be dismissed as a political question only if one of six formulations is 'inextricable from the case at bar.'</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>Six formulations: (1) a textually demonstrable commitment of the issue to a coordinate political department; (2) a lack of judicially discoverable and manageable standards; (3) the impossibility of deciding without an initial policy determination clearly for nonjudicial discretion; (4) the impossibility of independent resolution without expressing lack of respect due coordinate branches; (5) an unusual need for unquestioning adherence to a political decision already made; (6) the potential embarrassment of multifarious pronouncements by various departments on one question. Nonjusticiability is primarily a function of separation of powers.</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>• The doctrine concerns 'political questions,' not 'political cases': courts cannot refuse a bona fide controversy over whether 'political' action exceeds constitutional authority
 • Requires 'discriminating inquiry into the precise facts and posture' of each case, not 'semantic cataloguing'
@@ -2509,47 +2982,47 @@
 • Builds on Coleman v. Miller's two 'dominant considerations': finality of political action and lack of judicial criteria</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr">
         <is>
           <t>Baker is the framework for every political question answer: run the facts through the formulations, leading with the first two. Counterpoint: the Reader Comment's tests-versus-factors debate and Powell's three-question restatement in Goldwater.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
+    <row r="54">
+      <c r="A54" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>Nixon v. United States (1993)</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Political question: impeachment</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Federal judge Walter Nixon was impeached and convicted after a Senate committee under Rule XI heard the evidence and reported a transcript to the full Senate. He sued, claiming he was not 'tried' by the full Senate.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Nixon's challenge to Rule XI under the Impeachment Trial Clause is a nonjusticiable political question.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>Textual commitment and lack of manageable standards work together: 'sole Power to try' commits impeachment trials to the Senate alone, and 'try' gives no judicially manageable standard. Courts still review action that crosses 'identifiable textual limits' (oath, two-thirds vote, Chief Justice presiding when the President is tried).</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>• 'Sole' means the Senate acts 'independently and without assistance or interference'; the Committee of Style argument that 'sole' was cosmetic failed
 • No judicial role because impeachment and criminal trial are separate proceedings (bias risk) and impeachment is the Legislature's only check on the Judiciary; Senate abuse is checked by House/Senate division and the two-thirds rule
@@ -2557,47 +3030,47 @@
 • White (with Blackmun): justiciable, 'try' is no harder than 'due process,' but the Senate did try Nixon; Souter: nonjusticiable on prudential grounds, but a 'coin toss' or 'bad guy' conviction might warrant review</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr">
         <is>
           <t>Nixon is the leading example of Baker factors 1 and 2 applied together. For a hypo, contrast the majority (no review) with White and Souter (review of extreme cases).</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
+    <row r="55">
+      <c r="A55" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>Goldwater v. Carter (D.C. Cir. en banc 1979; U.S. 1979)</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Political question: foreign affairs</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>President Carter recognized the People's Republic of China and gave one-year notice terminating the Mutual Defense Treaty with Taiwan under its termination clause, without Senate or congressional consent. Senator Goldwater and other legislators sued.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>The D.C. Circuit en banc upheld the President's notice on the merits; the Supreme Court, with no majority opinion, vacated and remanded with directions to dismiss the complaint.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>No single rationale controls. Rehnquist (four Justices): a nonjusticiable political question because the Constitution is silent on treaty termination and foreign relations are involved. Powell: not ripe until each branch takes official action and reaches a 'constitutional impasse.'</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>• D.C. Cir.: the treaty's termination clause was 'an overarching factor' and the President's authority 'at its zenith'; MacKinnon would find the case justiciable but deny the President sole power
 • Rehnquist analogized Coleman v. Miller (Art. V silent on rejection), distinguished Youngstown (private litigants, domestic impact), and vacated so the ruling would not 'spawn any legal consequences' (Munsingwear)
@@ -2605,327 +3078,511 @@
 • Brennan would affirm on the recognition power: which branch holds a power is a legal question for courts; reader asks 'What is the controlling opinion?' Answer: none</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr">
         <is>
           <t>Use Goldwater to contrast political question (Rehnquist) with ripeness (Powell). For a legislator suit where Congress has not voted, Powell's approach says dismiss as unripe.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
+    <row r="56">
+      <c r="A56" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>Vieth v. Jubelirer (2004)</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Political question doctrine</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>The reader excerpt omits the facts and gives only the plurality's discussion of Baker.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>The reader excerpt gives no disposition; the plurality relied on Baker's second test, the lack of judicially discoverable and manageable standards.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>Baker's six 'independent tests' are 'probably listed in descending order of both importance and certainty,' and the second is valid because 'the judicial Power' is the traditional power of courts, which must act by principled rule.</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>• Called Baker's list 'tests,' not factors (contrast Sotomayor's 'factors' in Zivotofsky)
 • Legislative law may be 'inconsistent, illogical, and ad hoc'; law from courts 'must be principled, rational, and based upon reasoned distinctions'
 • Plurality opinion only; Kennedy concurred in the judgment and the separate opinions are omitted</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr">
         <is>
           <t>Use Vieth to explain why manageable standards matter: judicial legitimacy depends on rules. Pair it with the Reader Comment on tests versus factors.</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
+    <row r="57">
+      <c r="A57" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>Frederick v. Biden (S.D.N.Y. 2023)</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Standing; political question</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>A pro se plaintiff asked the court to have the House impeach and jail President Biden, 'put [Donald] Trump back in office,' and claw back spending he disagreed with.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Dismissed for lack of subject matter jurisdiction because the plaintiff lacked standing and the claims raised political questions; leave to amend was denied as futile.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>Disagreement with an official's policies is a generalized grievance, not a concrete and particularized injury (TransUnion's three elements). Policy choices committed to Congress or the Executive are political questions (Japan Whaling).</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>• Two independent grounds: no standing AND political question
 • Standing focuses on the party; the political question doctrine focuses on the issue (DaCosta v. Laird)
 • Both doctrines come from Article III's case-or-controversy language</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr">
         <is>
           <t>A clean modern example of both justiciability doctrines working together. For a client hypo about forcing an impeachment, cite it for dismissal on both grounds.</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="4" t="n">
+    <row r="58">
+      <c r="A58" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>The Federalist No. 63 (1788)</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D58" s="4" t="inlineStr">
         <is>
           <t>Senate and state sovereignty</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="E58" s="4" t="inlineStr">
         <is>
           <t>Madison's essay on the Senate.</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="F58" s="4" t="inlineStr">
         <is>
           <t>Not a decision.</t>
         </is>
       </c>
-      <c r="G48" s="4" t="inlineStr">
+      <c r="G58" s="4" t="inlineStr">
         <is>
           <t>Election of senators by state legislatures gives the States an agency in the federal government, 'a convenient link between the two systems.' Equal state votes in the Senate recognize and preserve the States' 'residuary sovereignty.'</t>
         </is>
       </c>
-      <c r="H48" s="4" t="inlineStr">
+      <c r="H58" s="4" t="inlineStr">
         <is>
           <t>• Equal vote is 'at once a constitutional recognition of the portion of sovereignty remaining in the individual states, and an instrument for preserving that residuary sovereignty'
 • The 'diseases' governments are most liable to: 'the facility and excess of law-making'</t>
         </is>
       </c>
-      <c r="I48" s="4" t="inlineStr">
+      <c r="I58" s="4" t="inlineStr">
         <is>
           <t>Use it for the political safeguards of federalism: the States were protected through their role in forming the federal government.</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="4" t="n">
+    <row r="59">
+      <c r="A59" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>The Federalist No. 81 (1788)</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>State sovereign immunity</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="E59" s="4" t="inlineStr">
         <is>
           <t>Hamilton's essay on the judiciary, including original jurisdiction and suits against States.</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="F59" s="4" t="inlineStr">
         <is>
           <t>Not a decision.</t>
         </is>
       </c>
-      <c r="G49" s="4" t="inlineStr">
+      <c r="G59" s="4" t="inlineStr">
         <is>
           <t>'It is inherent in the nature of sovereignty, not to be amenable to the suit of an individual without its consent.' Unless surrendered in the plan of the Convention, that immunity stays with the States.</t>
         </is>
       </c>
-      <c r="H49" s="4" t="inlineStr">
+      <c r="H59" s="4" t="inlineStr">
         <is>
           <t>• Suits against States for debts would be pointless because recoveries could not be enforced 'without waging war against the contracting state'
 • States get original Supreme Court jurisdiction because it 'would ill suit its dignity to be turned over to an inferior tribunal'
 • Quoted by Hans, Alden and Allen; source of the 'plan of the Convention' idea later used in Katz, PennEast and Torres</t>
         </is>
       </c>
-      <c r="I49" s="4" t="inlineStr">
+      <c r="I59" s="4" t="inlineStr">
         <is>
           <t>The founding text for immunity and its exceptions: cite it for the default rule and for the 'surrender in the plan of the Convention' exception.</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="4" t="n">
+    <row r="60">
+      <c r="A60" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>Guthrie, The Eleventh Article of Amendment (1908)</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>Eleventh Amendment history</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>A 1908 Columbia Law Review article tracing state suability from ratification through Chisholm and the Eleventh Amendment.</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="F60" s="4" t="inlineStr">
         <is>
           <t>Not a decision.</t>
         </is>
       </c>
-      <c r="G50" s="4" t="inlineStr">
+      <c r="G60" s="4" t="inlineStr">
         <is>
           <t>Founding views conflicted: Hamilton, Madison and Marshall said States were not suable by individuals, while Pendleton, Henry and Mason (some as an objection) and Wilson and Randolph read Article III to allow it.</t>
         </is>
       </c>
-      <c r="H50" s="4" t="inlineStr">
+      <c r="H60" s="4" t="inlineStr">
         <is>
           <t>• Chisholm was an assumpsit suit for a debt under the Supreme Court's original jurisdiction; Iredell alone dissented
 • The amendment resolution came two days after Chisholm; Adams declared it ratified in 1798
 • Georgia's reported death-penalty statute has no record; probably a bill that passed only the lower house</t>
         </is>
       </c>
-      <c r="I50" s="4" t="inlineStr">
+      <c r="I60" s="4" t="inlineStr">
         <is>
           <t>Use Guthrie as the counterpoint to Hans and Alden: the founding record was divided, not a settled consensus for immunity.</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="4" t="n">
+    <row r="61">
+      <c r="A61" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>Reader Comment on Baker (tests vs. factors)</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>Political question doctrine</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>A short reader note following Vieth.</t>
         </is>
       </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t>Not a decision.</t>
         </is>
       </c>
-      <c r="G51" s="4" t="inlineStr">
+      <c r="G61" s="4" t="inlineStr">
         <is>
           <t>The Vieth plurality calls Baker's list six 'tests'; Sotomayor in Zivotofsky v. Clinton (2012) calls them 'factors.' In practice the Court discusses only the first two (textual commitment; no manageable standards).</t>
         </is>
       </c>
-      <c r="H51" s="4" t="inlineStr">
+      <c r="H61" s="4" t="inlineStr">
         <is>
           <t>• Tests suggest any one is decisive; factors suggest weighing
 • Zivotofsky quotes Nixon quoting Baker for the first two only</t>
         </is>
       </c>
-      <c r="I51" s="4" t="inlineStr">
+      <c r="I61" s="4" t="inlineStr">
         <is>
           <t>Use it to argue the doctrine has narrowed to textual commitment and manageable standards, with the prudential factors (Souter in Nixon) on the margins.</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="n">
+    <row r="62">
+      <c r="A62" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>Moore's Federal Practice: political question sections</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>Political question treatise</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>Assigned sections on the doctrine and Baker's elements.</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>Not all of Baker's elements carry equal weight.</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>Covers the nature of the doctrine (§ 101.110), Baker's elements (§ 101.112) and that not all elements are equal (§ 101.114).</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>• Only the first two Baker factors (textual commitment; no manageable standards) do real work in later cases</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>Use with the reader comment on Baker (tests vs. factors) and Vieth's "descending order."</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>Goldwater v. Carter background documents</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>Treaty termination</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>President Carter's statements on recognizing the PRC and the Taiwan Relations Act.</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>On Dec. 15, 1978, the U.S. announced recognition of the PRC as the sole government of China and notice terminating the Mutual Defense Treaty with Taiwan.</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>The Taiwan Relations Act (1979) kept unofficial relations through the American Institute in Taiwan.</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>• The treaty was ended by presidential notice under its own termination clause (Article X), which is what the senators challenged</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>Factual setting for Goldwater's political-question and ripeness opinions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>Article III, Section 2 (text)</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>Judicial power: text</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>The constitutional text listing the cases and controversies federal courts may hear.</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>Extends the judicial power to listed controversies, including those "between a State and Citizens of another State."</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>Gives the Supreme Court original jurisdiction in cases involving States and ambassadors, and appellate jurisdiction "with such Exceptions, and under such Regulations as the Congress shall make."</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>• The state-citizen clause is what Chisholm applied and the Eleventh Amendment cut back
+• The Exceptions Clause is the basis for McCardle
+• Marbury: Congress can't add to original jurisdiction</t>
+        </is>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>Anchor text for Chisholm, Hans, McCardle and Marbury.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>CRS Report R45323: Eleventh Amendment and State Sovereign Immunity (2023)</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>Sovereign immunity</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>A CRS summary of state sovereign immunity doctrine.</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>"Eleventh Amendment immunity" is "something of a misnomer": the immunity neither derives from nor is limited by the Amendment's text.</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>States may be sued only by (1) waiver/consent, unequivocally expressed (including as a clear condition on federal funds, e.g., IDEA); (2) structural waiver in the plan of the Convention (suits between States or by the U.S.; Bankruptcy, eminent domain, armed forces); (3) abrogation: "unmistakably clear" language plus a valid power, chiefly § 5 of the Fourteenth Amendment, not Article I; and Ex parte Young for prospective relief against officers.</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>• Two imperatives: the States' dignity and financial solvency
+• Immunity reaches suits by a State's own citizens, suits in state courts, and federal agency adjudication
+• Ex parte Young is "narrow": no damages from the treasury, prospective only</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>The cleanest summary for a sovereign-immunity essay; pair with Hans, Alden, Allen v. Cooper, Torres, Edelman.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>Gibbons v. Ogden (1824)</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Commerce Clause</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>New York laws granted an exclusive steamboat privilege, enforced by a New York decree against the appellant, who claimed the laws conflicted with the commerce power and with an act of Congress licensing vessels.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>The New York laws, as applied to vessels licensed under the federal act, collide with federal law and must yield under the Supremacy Clause.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>Commerce is 'traffic, but it is something more: it is intercourse,' including navigation. 'Among the several States' means 'intermingled with' and reaches commerce that concerns more States than one, but not the 'completely internal commerce of a State.' The power to regulate is 'complete in itself' and limited mainly by political checks.</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>• Rejected strict construction; 'the enumeration presupposes something not enumerated'
 • Restraints on Congress are political: the people's influence at elections, not courts
@@ -2933,47 +3590,47 @@
 • Licensed steamboats can no more be restrained 'than if they were wafted on their voyage by the winds'</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr">
         <is>
           <t>Gibbons is the broad starting point that Wickard says was 'restored' and Lopez cites for limits ('the enumeration presupposes something not enumerated'). Use it both ways.</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="n">
+    <row r="67">
+      <c r="A67" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>A. L. A. Schechter Poultry Corp. v. United States (1935)</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Commerce Clause: direct/indirect</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Brooklyn slaughterhouses that bought poultry shipped from other States and sold only to local retailers were convicted of violating the NIRA Live Poultry Code's wage, hour and trade rules.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>The code provisions were invalid as an unconstitutional delegation and as regulation of intrastate transactions that affect interstate commerce only indirectly; convictions reversed.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>Congress may reach intrastate activity with direct effects on interstate commerce but not indirect ones; the distinction is 'essential to the maintenance of our constitutional system.' Once goods come to 'permanent rest' in a State, the stream of commerce ends.</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>• 'Extraordinary conditions do not create or enlarge constitutional power'
 • The government's wage argument 'proves too much': it would reach rents, advertising and every cost
@@ -2981,94 +3638,94 @@
 • Goods only resting temporarily before moving on stay in the stream; Wickard abandoned the direct/indirect label but did not expressly overrule Schechter</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr">
         <is>
           <t>Schechter marks the pre-1937 limit. Contrast Wickard's substantial-effects test; Lopez and Morrison later borrow its worry that federal power could reach everything.</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="n">
+    <row r="68">
+      <c r="A68" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>United States v. Butler (1936)</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Spending Clause</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>The reader excerpt omits the facts; it gives only the Court's discussion of the power to tax and spend for the general welfare.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>The Court adopted the Hamiltonian view that the power to spend for the general welfare is not limited to the enumerated powers (per O'Connor in Dole, Butler then struck down the Agricultural Adjustment Act as regulation).</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>Spending for public purposes 'is not limited by the direct grants of legislative power,' but must serve the general, national welfare and not local purposes.</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>• Madison: General Welfare Clause only refers to other enumerated powers ('mere tautology'); Hamilton: a separate power limited by the general welfare; Court adopted Story's Hamiltonian view
 • The Court's 'only one duty': lay the Constitution beside the statute and see if it 'squares'
 • Dole relies on Butler; O'Connor calls Butler the last case striking down an Act under the Spending Clause and blames its 'crabbed view' of commerce, not its spending analysis</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr">
         <is>
           <t>Butler is the foundation for conditional spending: Congress may pursue ends it cannot regulate directly. Pair it with Dole's limits.</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
+    <row r="69">
+      <c r="A69" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>Wickard v. Filburn (1942)</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Commerce Clause: aggregation</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Ohio farmer Filburn grew wheat beyond his AAA quota, using the excess on his farm for feed, flour and seed, and was assessed a marketing penalty.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Congress could apply wheat marketing quotas to wheat grown for consumption on the farm.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>Even local, noncommercial activity may be reached if it 'exerts a substantial economic effect on interstate commerce,' whatever it is called. A trivial individual effect counts when, 'taken together with that of many others similarly situated,' it is 'far from trivial.'</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>• Home-grown wheat 'competes with wheat in commerce': it supplies needs otherwise met by purchases and can flow into the market
 • Direct/indirect and labels like production or consumption are no longer controlling
@@ -3076,47 +3733,47 @@
 • Lopez calls it 'perhaps the most far reaching example' but still economic activity; Raich reaffirmed it</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr">
         <is>
           <t>Wickard is the aggregation case: use it for any home-production hypo. Counterpoint: Morrison refuses to aggregate noneconomic violence, and O'Connor in Raich says Wickard did not reach 'the home cook's herb garden.'</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
+    <row r="70">
+      <c r="A70" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>Allen v. Cooper (2020)</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Sovereign immunity: abrogation</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>A videographer who documented the Blackbeard shipwreck owned by North Carolina sued the State after it posted five of his videos online and used one of his photos in a newsletter, relying on the Copyright Remedy Clarification Act's abrogation of immunity.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>The CRCA did not validly abrogate state immunity: the Intellectual Property Clause cannot support abrogation, and Section 5 could not on this legislative record.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>Abrogation requires (1) unequivocal statutory language and (2) a valid constitutional authority. Article I generally cannot be used to circumvent state immunity (Seminole Tribe; Florida Prepaid).</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>• 'Florida Prepaid all but prewrote our decision today'; overruling it needed a 'special justification' that Allen did not offer
 • Katz is 'bankruptcy exceptionalism,' a 'good-for-one-clause-only holding': the Bankruptcy Clause itself abrogated in the plan of the Convention
@@ -3124,47 +3781,47 @@
 • Clear statement was undisputed; the case turned on the source of power</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr">
         <is>
           <t>Allen sets the two-step abrogation test and treats Katz as unique. Counterpoint: Torres and Kagan's concurrence ('PennEast proved me wrong') widened the plan-of-the-Convention route.</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
+    <row r="71">
+      <c r="A71" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>Torres v. Texas Department of Public Safety (2022)</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Sovereign immunity: structural waiver</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>An Army reservist who returned from Iraq with constrictive bronchitis from burn pits sued Texas in state court under USERRA after the State refused to reemploy him in a different role.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>States cannot invoke sovereign immunity to block USERRA suits because they agreed in the plan of the Convention that their sovereignty would yield to the federal power to raise and support armies.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>Structural waiver applies when the federal power is 'complete in itself, and the States consented to the exercise of that power, in its entirety, in the plan of the Convention' (PennEast). States may be sued by consent, by Section 5 abrogation, or by such structural waiver.</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>• Recognized structural waivers: suits between States, suits by the U.S., bankruptcy (Katz), eminent domain (PennEast), and now the military powers
 • Distinguished Seminole Tribe and Florida Prepaid: those powers are not denied to the States or essential to the Union's survival
@@ -3172,47 +3829,47 @@
 • State courts may not apply a state immunity statute to block the federal claim (Supremacy Clause; Testa v. Katt)</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr">
         <is>
           <t>Torres shows the plan-of-the-Convention exception swallowing part of Alden. Use it against Seminole Tribe and Allen to sort which Article I powers can support private suits.</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
+    <row r="72">
+      <c r="A72" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>Virginia Office for Protection &amp; Advocacy v. Stewart (2011)</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Sovereign immunity: Ex parte Young</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>A Virginia agency created by state law and authorized to sue state officials brought a federal suit for prospective relief against officials of state-run mental hospitals.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Ex parte Young allows the suit; the Eleventh Amendment does not bar an agency of the same State from invoking federal jurisdiction against state officials.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>Young rests on the 'fiction' that an official ordered only to stop violating federal law is not the State. It does not apply when the State is the real party in interest, as when the judgment would expend itself on the public treasury or domain.</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>• The Amendment's text 'only eliminates the basis for our judgment' in Chisholm; since Hans it confirms a structural immunity
 • Virginia's own law created the agency and let it sue, so it proceeds 'on the same terms as any other litigant'
@@ -3220,140 +3877,326 @@
 • Restates the defaults: States may waive; Congress may abrogate under Section 5 but not Article I commerce power</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr">
         <is>
           <t>VOPA extends Young to an unusual plaintiff while restating its limits. Use it with Edelman to separate permitted prospective relief from barred treasury relief.</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="4" t="n">
+    <row r="73">
+      <c r="A73" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C73" s="5" t="inlineStr">
         <is>
           <t>The Federalist Nos. 51 and 71 (1788)</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D73" s="4" t="inlineStr">
         <is>
           <t>Separation of powers</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="E73" s="4" t="inlineStr">
         <is>
           <t>Assigned excerpts: Madison on legislative predominance and Hamilton on the executive's duty to the public.</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="F73" s="4" t="inlineStr">
         <is>
           <t>Not a decision.</t>
         </is>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G73" s="4" t="inlineStr">
         <is>
           <t>Fed. 51: 'In republican government the legislative authority, necessarily, predominates.' Fed. 71: the 'deliberate sense of the community' should govern, not 'every sudden breese of passion.'</t>
         </is>
       </c>
-      <c r="H59" s="4" t="inlineStr">
+      <c r="H73" s="4" t="inlineStr">
         <is>
           <t>• Fed. 71: officials should 'withstand the temporary delusion' to allow 'more cool and sedate reflection'
 • The people 'commonly intend the PUBLIC GOOD' but sometimes err about the means</t>
         </is>
       </c>
-      <c r="I59" s="4" t="inlineStr">
+      <c r="I73" s="4" t="inlineStr">
         <is>
           <t>Use for the theme that the Constitution filters popular passion, for example when defending deliberate political checks over courts.</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="4" t="n">
+    <row r="74">
+      <c r="A74" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>The Federalist Nos. 14, 36 and 45 (1787-1788)</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D74" s="4" t="inlineStr">
         <is>
           <t>Commerce power: founding</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="E74" s="4" t="inlineStr">
         <is>
           <t>Assigned excerpts from Madison (14, 45) and Hamilton (36) bearing on the commerce power.</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr">
+      <c r="F74" s="4" t="inlineStr">
         <is>
           <t>Not a decision.</t>
         </is>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="G74" s="4" t="inlineStr">
         <is>
           <t>Fed. 45: federal powers are 'few and defined,' and the commerce power is 'a new power' that 'few oppose.' Fed. 36 is included to show Hamilton treated agriculture, commerce and manufacturing as different activities.</t>
         </is>
       </c>
-      <c r="H60" s="4" t="inlineStr">
+      <c r="H74" s="4" t="inlineStr">
         <is>
           <t>• Reader Comment: Fed. 36 is there only to show farming, commerce and manufacturing as distinct (used by Thomas in Lopez)
 • Fed. 45 opens Lopez and is quoted in O'Connor's Raich dissent
 • Fed. 14 answers the objection from the country's great extent: roads, canals and navigation will ease intercourse</t>
         </is>
       </c>
-      <c r="I60" s="4" t="inlineStr">
+      <c r="I74" s="4" t="inlineStr">
         <is>
           <t>Use these for originalist limits on 'commerce' (Thomas in Lopez) and the 'few and defined' theme in Lopez and Raich.</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="n">
+    <row r="75">
+      <c r="A75" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>CALI Assessment: Eleventh Amendment</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>Sovereign immunity</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>A self-test on sovereign immunity.</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>The reader's note asks whether the "correct" answer to Question 4 fits Katz (2006), PennEast (2021) and Torres (2022).</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>Signals that structural-waiver cases have moved the doctrine since the assessment was written.</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>• The professor flags that the CALI answer may be outdated after the structural-waiver cases</t>
+        </is>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>Use to show awareness that Torres expanded structural waiver.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>Types of Legislation (Senate website)</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>Legislative process</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>The Senate's description of bills and resolutions.</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>Only bills and joint resolutions (other than proposed amendments) need the President's signature and have the force of law.</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>Bills (H.R./S.) and joint resolutions (H.J.Res./S.J.Res.): both houses plus President; joint resolutions are used for continuing or emergency appropriations. Joint resolutions proposing amendments: two-thirds of both houses and three-fourths of the States, no President. Concurrent resolutions (H.Con.Res./S.Con.Res.): both houses, no President, no force of law; used for adjournment, joint rules, and the budget resolution. Simple resolutions (H.Res./S.Res.): one house only.</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>• "Con" = both houses, no President
+• "J" = like a bill
+• Plain "Res" = one house
+• Setting adjournment is a concurrent resolution</t>
+        </is>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>Background for bicameralism and presentment arguments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>CRS, Recurring Constitutional Issues in Federal Legislation (2022)</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>Congress's powers: overview</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>A CRS checklist for evaluating federal legislation.</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>Every bill raises two questions: is it within an enumerated power, and does it violate another constraint (federalism, separation of powers, individual rights)?</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>Summarizes Lopez's categories, Dole's spending limits, Boerne's congruence and proportionality, anti-commandeering (Murphy v. NCAA), bicameralism and presentment (Chadha), and nondelegation (intelligible principle).</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>• The two-question framework
+• Dole's limits restated: clear notice, relatedness, no coercion, no independent bar</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>A ready-made structure for any "Is this statute constitutional?" essay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>CRS, Congress's Authority to Regulate Interstate Commerce (2021)</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>Commerce Clause: overview</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>A CRS survey of Commerce Clause doctrine.</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>Describes three eras: constrained (before the 1930s), expansive (mid-20th century), and limits since Lopez.</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>Lower courts weigh four substantial-effects factors: economic nature, jurisdictional element, findings, and the attenuation of the link. NFIB: no regulation of inactivity.</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>• Findings are neither necessary nor sufficient (Lopez; Morrison)
+• After Lopez, Congress added a jurisdictional element to the gun law, and lower courts uphold it (see Dorsey)
+• Examples of each Lopez category</t>
+        </is>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>Use for the arc of Commerce Clause doctrine in an essay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t>Perez v. United States (1971)</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Commerce Clause: class of activities</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Perez was convicted under the federal loan-sharking statute for extortionate collection from a local butcher shop owner, with no proof of interstate movement.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Congress could criminalize extortionate credit transactions, even purely local ones, under the Commerce Clause; conviction affirmed.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>The Commerce Clause reaches three categories: (1) use of the channels of commerce; (2) protection of instrumentalities and persons or things in commerce; (3) activities affecting commerce. When a class of activities is within federal power, courts may not 'excise, as trivial, individual instances' of the class.</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>• Category examples: shipping stolen goods (channels); destroying aircraft or thefts from interstate shipments (instrumentalities and things in commerce)
 • Congress need not make particularized findings, though here it found loan sharking funds national organized crime
@@ -3361,47 +4204,47 @@
 • Holmes in Westfall: Congress may 'embrace more than the precise thing to be prevented'</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr">
         <is>
           <t>Perez gives the three-category framework Lopez later refines, and its class-of-activities rule underlies Russell and Raich. Stewart's dissent previews Lopez's police-power concern.</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="n">
+    <row r="80">
+      <c r="A80" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>Hodel v. Virginia Surface Mining &amp; Reclamation Ass'n (1981)</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Commerce Clause: rational basis</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>In a pre-enforcement facial challenge to the Surface Mining Control and Reclamation Act of 1977, a federal district court in Virginia declared central provisions unconstitutional and enjoined them.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>On a facial challenge, the Act is a valid exercise of the commerce power and does not violate the Fifth or Tenth Amendments.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>When Congress finds an activity affects interstate commerce, courts ask only whether the finding is rational and whether the means are reasonable and appropriate. Preventing destructive interstate competition and multistate environmental harm are valid aims.</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>• Calling an activity 'local' or a 'land use' does not resolve the question
 • Rehnquist concurred only in the judgment: the test is substantial effect, not mere effect
@@ -3409,94 +4252,94 @@
 • Rehnquist called enumerated powers 'one of the greatest fictions' of the federal system</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr">
         <is>
           <t>Hodel is the deferential rational-basis case Souter cites in Lopez; Rehnquist's concurrence is the seed of Lopez and Morrison.</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="n">
+    <row r="81">
+      <c r="A81" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>Russell v. United States (1985)</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Commerce Clause: statutory reach</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Russell tried to have his two-unit Chicago rental building burned and was convicted under the federal arson statute covering property used in an activity affecting interstate commerce.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>A rental building is property used in an activity affecting commerce, so the statute applied; conviction affirmed.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>The rental of real estate is 'unquestionably' an activity affecting commerce; a local rental is an element of a broader commercial rental market, and power over the class reaches individual activity within it (Perez). The phrase 'any activity affecting interstate or foreign commerce' signals use of Congress's full commerce power.</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>• Congress dropped 'for business purposes'; Rep. Celler said bombing a private home would not be covered because of doubts about congressional power
 • Comment: Saneii v. Robards (W.D. Ky. 2003) held a residential real estate sale outside the commerce power for Federal Arbitration Act purposes because land is 'inherently intrastate'
 • Professor's question: can Saneii be reconciled with Russell? Tension: Russell views one rental as part of a broad market; Saneii viewed one sale alone</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr">
         <is>
           <t>Russell shows the class-of-activities rule applied to real estate. Use Saneii as the counterpoint for owner-occupied or one-off property transactions.</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="n">
+    <row r="82">
+      <c r="A82" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t>South Dakota v. Dole (1987)</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Spending Clause conditions</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>South Dakota let 19-year-olds buy 3.2% beer. A federal law withheld 5% of certain highway funds from States allowing purchase of alcohol by anyone under 21.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>The condition was a valid use of the spending power, whether or not Congress could set a drinking age directly.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>Conditions on federal funds must (1) serve the general welfare; (2) be unambiguous; (3) relate to the federal interest in the particular national project; and (4) not be barred by another constitutional provision. Inducement also may not be so coercive that 'pressure turns into compulsion.'</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>• The independent-bar limit only stops Congress from inducing States to do something itself unconstitutional (e.g., cruel and unusual punishment); spending may pursue ends Congress cannot reach directly (Butler)
 • Losing 5% was 'relatively mild encouragement'; success in getting States to comply does not make a condition coercive
@@ -3504,47 +4347,47 @@
 • O'Connor dissent: the condition is not reasonably related to highway spending; a condition must say how money is spent, anything more is regulation; state-capital hypothetical</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr">
         <is>
           <t>Dole is the spending route around Lopez (see Clinton and Reagan). For a hypo, run all four limits plus coercion; O'Connor's relatedness test is the counterargument.</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="n">
+    <row r="83">
+      <c r="A83" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
         <is>
           <t>United States v. Lopez (1995)</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Commerce Clause limits</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>A 12th-grader brought a concealed handgun to his San Antonio high school and was charged under the Gun-Free School Zones Act of 1990.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>The Act exceeds the commerce power because it neither regulates commercial activity nor requires a connection between the gun possession and interstate commerce.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>Congress may regulate (1) the use of the channels of interstate commerce; (2) the instrumentalities of interstate commerce, or persons or things in interstate commerce; and (3) activities that substantially affect interstate commerce. Under the third, the Court looks at whether the activity is economic, whether there is a jurisdictional element, whether there are findings, and how attenuated the link is.</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>• The test is 'substantially affects,' not merely 'affects'; only category 3 could apply
 • Rejected the government's cost-of-crime and national-productivity theories as 'pil[ing] inference upon inference' toward a general police power
@@ -3552,47 +4395,47 @@
 • Kennedy: stare decisis bars a return to an 18th-century view; federalism is the Framers' 'unique contribution.' Thomas: original 'commerce' means buying, selling, bartering and transport. Breyer: cumulative effect plus rational basis. Souter: 'Not every epochal case has come in epochal trappings'</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr">
         <is>
           <t>Lopez is the first modern limit on the commerce power. Fixes: add a jurisdictional element (Clinton's 1996 amendment) or use spending (Dole); counterpoint is Raich's broad reading for economic schemes.</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="n">
+    <row r="84">
+      <c r="A84" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t>United States v. Morrison (2000)</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Commerce Clause limits</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>A Virginia Tech student alleged two football players raped her and sued them under the Violence Against Women Act's federal civil remedy for gender-motivated violence.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>The civil remedy exceeds Congress's power under both the Commerce Clause and Section 5 of the Fourteenth Amendment.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>Congress may not regulate noneconomic, violent criminal conduct based solely on its aggregate effect on interstate commerce. Congressional findings are not sufficient by themselves; whether an activity substantially affects commerce is ultimately a judicial question.</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>• Findings relied on the 'but-for causal chain' Lopez rejected, which would let Congress regulate all violent crime and family law
 • The Court did NOT adopt a categorical rule against aggregating noneconomic activity, but has upheld only economic activity 'thus far'
@@ -3600,47 +4443,47 @@
 • Souter dissent: a 'mountain of data' and rational-basis review make the result irreconcilable with precedent; Thomas would scrap the substantial effects test</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr">
         <is>
           <t>Morrison confirms Lopez even with extensive findings. For hypos, a jurisdictional hook (e.g., violence against persons traveling in interstate commerce) makes a statute stronger.</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="n">
+    <row r="85">
+      <c r="A85" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
         <is>
           <t>Gonzales v. Raich (2005)</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Commerce Clause: economic class</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>California medical marijuana patients, acting lawfully under state law, had their homegrown plants seized by federal agents and sought to bar enforcement of the Controlled Substances Act.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>The Controlled Substances Act validly applies to local cultivation and use of marijuana that complies with California law.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>Congress may regulate purely local activities that are part of an economic 'class of activities' that substantially affects interstate commerce, and the Court asks only whether a rational basis exists. Failure to regulate would leave 'a gaping hole' in a comprehensive scheme.</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>• Follows Wickard: a fungible commodity with an established interstate market; illegality of the market does not matter
 • Distinguished Lopez and Morrison: those were challenges to whole statutes; Lopez was a 'brief, single-subject statute,' while the CSA regulates 'quintessentially economic' activity
@@ -3648,186 +4491,186 @@
 • O'Connor: 'perverse incentive' to bury local regulation in big schemes, making Lopez 'nothing more than a drafting guide'; daycare/charades substitutes example. Thomas: the marijuana was 'neither interstate nor commerce'</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr">
         <is>
           <t>Raich shows Lopez's limit is narrow when the activity sits inside a comprehensive economic scheme. State-law compliance does not matter under the Supremacy Clause; relief lies in rescheduling or the democratic process.</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="4" t="n">
+    <row r="86">
+      <c r="A86" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B86" s="4" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C86" s="5" t="inlineStr">
         <is>
           <t>Clinton's response to Lopez (1995) and the 1996 amendment</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D86" s="4" t="inlineStr">
         <is>
           <t>Commerce Clause: legislative response</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="E86" s="4" t="inlineStr">
         <is>
           <t>After Lopez, President Clinton responded in a radio address and a message to Congress, and Congress later amended the Gun-Free School Zones Act.</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr">
+      <c r="F86" s="4" t="inlineStr">
         <is>
           <t>Not a decision.</t>
         </is>
       </c>
-      <c r="G68" s="4" t="inlineStr">
+      <c r="G86" s="4" t="inlineStr">
         <is>
           <t>Clinton directed the Attorney General to report within a week, suggested tying federal funds to state school-zone gun bans, and sent Congress a bill adding a jurisdictional element. The 1996 amendment made it unlawful to possess 'a firearm that has moved in or that otherwise affects interstate or foreign commerce' in a school zone.</t>
         </is>
       </c>
-      <c r="H68" s="4" t="inlineStr">
+      <c r="H86" s="4" t="inlineStr">
         <is>
           <t>• Both fixes track Lopez: a jurisdictional element (category 3 nexus) and a spending-power route (Dole)
 • Reno: little prosecutorial impact because most guns have moved in commerce; no need to prove the defendant knew of the commerce link
 • CRS: the Supreme Court has not revisited the amended law; lower courts generally uphold it</t>
         </is>
       </c>
-      <c r="I68" s="4" t="inlineStr">
+      <c r="I86" s="4" t="inlineStr">
         <is>
           <t>Use it to show how Congress can respond to Lopez: add a jurisdictional hook or condition federal funds.</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="4" t="n">
+    <row r="87">
+      <c r="A87" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="B87" s="4" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C87" s="5" t="inlineStr">
         <is>
           <t>Reagan, Remarks at River Dell High School (1984)</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="D87" s="4" t="inlineStr">
         <is>
           <t>Spending Clause conditions</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
+      <c r="E87" s="4" t="inlineStr">
         <is>
           <t>President Reagan's remarks supporting the federal drinking-age legislation later upheld in South Dakota v. Dole.</t>
         </is>
       </c>
-      <c r="F69" s="4" t="inlineStr">
+      <c r="F87" s="4" t="inlineStr">
         <is>
           <t>Not a decision.</t>
         </is>
       </c>
-      <c r="G69" s="4" t="inlineStr">
+      <c r="G87" s="4" t="inlineStr">
         <is>
           <t>Reagan backed withholding 5% of highway funds from States without a 21-year-old drinking age, because the 'crazy-quilt' of state laws created 'Blood Borders' as teenagers drove to lower-age States.</t>
         </is>
       </c>
-      <c r="H69" s="4" t="inlineStr">
+      <c r="H87" s="4" t="inlineStr">
         <is>
           <t>• He reconciled this with 'State solutions' because drunk driving is a national problem involving travel across state borders and 'The choice remains with the States'
 • He did NOT claim Congress could set a drinking age directly
 • His Commission on Drunk Driving's findings reappear in Dole's relatedness analysis</t>
         </is>
       </c>
-      <c r="I69" s="4" t="inlineStr">
+      <c r="I87" s="4" t="inlineStr">
         <is>
           <t>Pair with Dole to show the political case for conditional spending: national problem, mild inducement, state choice preserved.</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="4" t="n">
+    <row r="88">
+      <c r="A88" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B70" s="4" t="inlineStr">
+      <c r="B88" s="4" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C88" s="5" t="inlineStr">
         <is>
           <t>Professor's note on Commerce Clause periods</t>
         </is>
       </c>
-      <c r="D70" s="4" t="inlineStr">
+      <c r="D88" s="4" t="inlineStr">
         <is>
           <t>Commerce Clause history</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
+      <c r="E88" s="4" t="inlineStr">
         <is>
           <t>A note on the CALI lesson 'The Early Commerce Clause' (Gibbons up to Lopez).</t>
         </is>
       </c>
-      <c r="F70" s="4" t="inlineStr">
+      <c r="F88" s="4" t="inlineStr">
         <is>
           <t>Not a decision.</t>
         </is>
       </c>
-      <c r="G70" s="4" t="inlineStr">
+      <c r="G88" s="4" t="inlineStr">
         <is>
           <t>The critical dividing line is 1937, not 1995. Three periods: Gibbons to 1937; 1937 to 1995; and 1995 (Lopez) to the present.</t>
         </is>
       </c>
-      <c r="H70" s="4" t="inlineStr">
+      <c r="H88" s="4" t="inlineStr">
         <is>
           <t>• Around 1937 the Court abandoned the direct/indirect limits (Jones &amp; Laughlin, then Wickard); Lopez left that era intact and overruled nothing</t>
         </is>
       </c>
-      <c r="I70" s="4" t="inlineStr">
+      <c r="I88" s="4" t="inlineStr">
         <is>
           <t>Use it to frame any Commerce Clause essay: Lopez trimmed the post-1937 expansion rather than reversing it.</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="n">
+    <row r="89">
+      <c r="A89" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t>NFIB v. Sebelius (2012)</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Commerce, Taxing and Spending Powers</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>The Affordable Care Act required individuals to buy health insurance or make a "shared responsibility payment" to the IRS, and threatened States with loss of all existing Medicaid funds unless they covered all nonelderly people below 133% of the poverty line. Florida and other States, individuals and the NFIB challenged both provisions.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>The mandate cannot be upheld under the Commerce or Necessary and Proper Clauses but is valid as a tax, and the Medicaid expansion is coercive only insofar as existing Medicaid funds may be withdrawn, so that sanction is barred and the rest of the Act stands.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>Commerce (Roberts): Congress may regulate existing activity but not compel individuals to enter commerce; "The Framers gave Congress the power to regulate commerce, not to compel it." Tax: substance controls over the "penalty" label; under the Drexel Furniture factors (not a heavy burden, no scienter, collected by the IRS) the payment is a tax, and the saving canon adopts any "fairly possible" constitutional reading. Spending: conditions on the use of new funds are valid, but threatening other significant independent grants turns "pressure into compulsion" ("a gun to the head," not Dole's "relatively mild encouragement").</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>• Necessary and Proper failed because the mandate is not "proper": it lets Congress create the predicate for exercising its own power; Raich distinguished
 • Roberts reached the commerce question only because the tax reading was a saving construction needed if the command failed; fn. 3: Ginsburg's other mandates (jury duty, draft) rest on powers other than commerce
@@ -3836,47 +4679,47 @@
 • Medicaid "shift in kind, not merely degree": original program covered four categories of the needy; expansion covers the entire nonelderly population below 133% of poverty; separate funding provision (90% for newly eligible vs. 50-83%); less comprehensive coverage. Congress had styled it a mere alteration of existing Medicaid; Roberts looked past the label</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
+      <c r="I89" s="2" t="inlineStr">
         <is>
           <t>Modern limit on the commerce power (activity versus inactivity) alongside Lopez and Morrison, and the first spending condition held coercive; counter with Ginsburg's view that the activity line is a "newly minted" formalism like the abandoned pre-New Deal categories.</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="n">
+    <row r="90">
+      <c r="A90" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>United States v. Dorsey (9th Cir. 2005)</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Commerce Clause: jurisdictional element</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Dorsey was convicted of possessing a firearm in a school zone in Anchorage under 18 U.S.C. § 922(q), which Congress amended after Lopez to cover only a firearm that "has moved in or that otherwise affects interstate or foreign commerce."</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>The amended § 922(q) is valid because its jurisdictional element ensures, case by case, that the possession affects interstate commerce, which "saves § 922(q) from the infirmity that defeated it in Lopez."</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>An express jurisdictional element tying each offense to interstate commerce brings a criminal statute within the commerce power (Bass, Scarborough). Lopez did not alter that rule, and Morrison noted that such an element was missing from the law it struck down.</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>• The cure for Lopez was the jurisdictional element, not congressional findings or a requirement that the defendant crossed state lines
 • Scarborough: "the minimal nexus that the firearm have been, at some time, in interstate commerce" suffices
@@ -3884,47 +4727,47 @@
 • Later abrogated by Arizona v. Gant on grounds unrelated to the Commerce Clause</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr">
         <is>
           <t>Shows Congress's response to Lopez: add a jurisdictional hook. Pair with Phomma, and contrast Willett's Bonner concurrence, which doubts that a minimal nexus meaningfully limits federal power over local possession.</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="n">
+    <row r="91">
+      <c r="A91" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>United States v. Phomma (D. Or. 2021)</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Commerce Clause: jurisdictional element</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Phomma was charged under the civil disorder statute, 18 U.S.C. § 231(a)(3), for spraying Portland police officers with bear spray during an August 2020 protest at the ICE building, where protesters blocked street traffic.</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>The motion to dismiss was denied because § 231(a)(3) has an express jurisdictional element requiring a civil disorder that "obstructs, delays, or adversely affects commerce."</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>Applying Lopez's three categories and Morrison's four factors (congressional findings, an express jurisdictional element, economic nature, attenuated link), a substantive express jurisdictional element keeps a criminal statute within the commerce power. The defendant cited no case striking down a statute that had one.</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>• Morrison's factors do NOT include whether the area is one the States traditionally regulate
 • The element must be substantive, not added just to ward off challenges; obstructing officers who are quelling a commerce-affecting disorder itself affects commerce (Howard)
@@ -3932,47 +4775,47 @@
 • A "civil disorder" requires an assemblage of three or more persons</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
+      <c r="I91" s="2" t="inlineStr">
         <is>
           <t>Applies Dorsey's jurisdictional-element reasoning to protest violence; also shows overlapping federal and state prosecution of the same conduct (Phomma faced parallel state charges).</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="n">
+    <row r="92">
+      <c r="A92" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
         <is>
           <t>United States v. Protho (7th Cir. 2022)</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Commerce Clause: instrumentalities</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Protho used his Ford Explorer to abduct a ten-year-old girl in Calumet City, Illinois, and was convicted under the Federal Kidnapping Act, which since 2006 covers use of "any means, facility, or instrumentality of interstate or foreign commerce." The jury was told that using an automobile satisfies that element.</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Conviction affirmed: automobiles are instrumentalities of interstate commerce, so the acquittal motion was properly denied and the jury was properly instructed.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>For the instrumentalities category, what matters is "the nature of the regulated object's class (here, automobiles) rather than the particular use of one member of that class"; no separate proof of interstate movement is required (Mandel).</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>• Rejected the argument that each car must be judged individually; a car that never left the State still qualifies
 • The evidence showed he drove interstate anyway, but the holding does not depend on that
@@ -3980,47 +4823,47 @@
 • Chavarria later distinguished it as a case about "automobiles," not all "motor vehicles"</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr">
+      <c r="I92" s="2" t="inlineStr">
         <is>
           <t>Represents the broad, class-based reading of Lopez's instrumentalities category; set it against Chavarria to show the circuit tension over how far that category reaches into local crime.</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="n">
+    <row r="93">
+      <c r="A93" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
         <is>
           <t>United States v. Chavarria (10th Cir. 2025)</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Commerce Clause: instrumentalities</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Chavarria and Romero allegedly kidnapped and murdered a woman in Eddy County, New Mexico. The federal kidnapping indictment alleged only that they "used a motor vehicle, a means, facility, and instrumentality of interstate commerce."</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Dismissal affirmed: "motor vehicles" are not per se instrumentalities of interstate commerce, so the "threadbare, conclusory" indictment was fatally deficient.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>An instrumentality of interstate commerce "must be a means to the end of commerce." Trains and aircraft qualify per se because they are used almost exclusively for commercial transport, but a generic class like motor vehicles (which includes e-bikes, lawnmowers and scooters) does not; holding otherwise would creep toward a general federal police power.</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>• Opens with then-Senator Biden: Congress federalizes "everything that walks, talks, and moves"; the government sought to add "everything that drives"
 • Distinguished Protho and Windham by level of generality (cars and automobiles versus motor vehicles) and called their rationales "perfunctory"
@@ -4028,47 +4871,47 @@
 • An indictment alleging the defendants crossed state lines, the evil the 1932 Act targeted, would likely stand</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
+      <c r="I93" s="2" t="inlineStr">
         <is>
           <t>The leading counterweight to Protho, grounded in the absence of a federal police power (Cohens v. Virginia, Federalist No. 17); use it to frame federalism as a question of who prosecutes, not whether the crime is punished.</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="n">
+    <row r="94">
+      <c r="A94" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
         <is>
           <t>United States v. Bonner (5th Cir. 2025)</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Commerce Clause: felon in possession</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Bonner, with prior drug-trafficking and felon-in-possession convictions, pleaded guilty to possessing a firearm as a felon under 18 U.S.C. § 922(g)(1) and challenged the statute under the Second Amendment, vagueness, the Commerce Clause and Equal Protection.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Affirmed per curiam: every challenge is foreclosed by Fifth Circuit precedent (Diaz on the Commerce Clause).</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>In the Fifth Circuit, § 922(g)(1) needs only a firearm made in one State and found in another, resting on Scarborough's minimal nexus. Willett, concurring, says a federal criminal statute must rest on an enumerated power and respect individual rights, and doubts § 922(g)(1) does either.</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>• Willett: mere possession fits uneasily in the Lopez categories because aggregation ordinarily requires economic activity
 • Willett: Scarborough was statutory construction that never mentioned the Commerce Clause, so it is "scant authority"
@@ -4076,47 +4919,47 @@
 • Willett still joined the majority because precedent controls, and asked the full court or the Supreme Court to reexamine</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr">
+      <c r="I94" s="2" t="inlineStr">
         <is>
           <t>Use as the critique of the jurisdictional-element cases: a minimal nexus may make the commerce power limitless. Contrast Dorsey and Phomma, which treat the element as enough.</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="n">
+    <row r="95">
+      <c r="A95" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
         <is>
           <t>McCulloch v. Maryland (1819)</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Necessary and Proper; state taxation</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Congress chartered the second Bank of the United States in 1816, and Maryland taxed banks operating in the State that its legislature had not chartered. John James, suing for himself and Maryland, won penalties under the act against McCulloch in Baltimore County court.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Congress had power to incorporate the Bank and its branches, and Maryland's tax on the Bank's operations was unconstitutional and void.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>McCulloch test: "Let the end be legitimate, let it be within the scope of the constitution, and all means which are appropriate, which are plainly adapted to that end, which are not prohibited, but consist with the letter and spirit of the constitution, are constitutional." "Necessary" means convenient, useful or conducive to, not absolutely necessary. States may not "retard, impede, burden, or in any manner control" valid federal laws, because "the power to tax involves the power to destroy."</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>• Art. I, § 10's "absolutely necessary" shows the framers knew how to demand strict necessity; the clause sits among Congress's powers, not its limits, and enlarges rather than restrains
 • The Tenth Amendment omits "expressly," so delegation depends on "a fair construction of the whole instrument"; incorporating a bank is a means, not "a great substantive and independent power"
@@ -4124,47 +4967,47 @@
 • Did NOT bar nondiscriminatory taxes on the Bank's real property or on Maryland citizens' interest in the Bank</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
+      <c r="I95" s="2" t="inlineStr">
         <is>
           <t>Foundation for implied powers and deference on the choice of means ("it is a constitution we are expounding"); NFIB used its "great substantive and independent power" limit and its pretext caveat to show the Court still polices the ends.</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="n">
+    <row r="96">
+      <c r="A96" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
         <is>
           <t>Dean Milk Co. v. Madison (1951)</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Dormant Commerce Clause: discrimination</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Madison, Wisconsin barred selling milk as pasteurized unless it was processed at an approved plant within five miles of the city center. Dean Milk, an Illinois company selling Grade A milk from plants 65 and 85 miles away, was denied a license solely because of that distance.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>The five-mile rule plainly discriminates against interstate commerce and is invalid because reasonable nondiscriminatory alternatives could protect health.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>A locality may not discriminate against interstate commerce, even to protect health and safety, "if reasonable nondiscriminatory alternatives, adequate to conserve legitimate local interests, are available." One State "may not place itself in a position of economic isolation" (Baldwin v. Seelig).</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>• Alternatives: inspect distant sources and charge importers the actual cost, or rely on producing-area ratings under the Public Health Service Model Milk Ordinance
 • A law is not valid just because it "professes to be a health measure," or the Clause would bite only when a State "artlessly discloses" discriminatory purpose
@@ -4172,47 +5015,47 @@
 • Madison's own Health Commissioner testified that either approach would adequately protect consumers</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr">
+      <c r="I96" s="2" t="inlineStr">
         <is>
           <t>Classic statement of the alternatives test for discriminatory laws; contrast Maine v. Taylor, where no adequate nondiscriminatory alternative existed and the ban survived.</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="n">
+    <row r="97">
+      <c r="A97" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
         <is>
           <t>Pike v. Bruce Church (1970)</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Dormant Commerce Clause: Pike balancing</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Arizona ordered Bruce Church to stop shipping its high-quality cantaloupes uncrated from its Parker, Arizona ranch to its packing shed in Blythe, California, and to pack them in Arizona instead. Compliance meant building a $200,000 packing shed for a crop worth $700,000.</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>The order is invalid because Arizona's "tenuous interest" in having the cantaloupes identified as Arizona's cannot justify requiring an unneeded in-state packing plant.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>Pike balancing: "Where the statute regulates even-handedly to effectuate a legitimate local public interest, and its effects on interstate commerce are only incidental, it will be upheld unless the burden imposed on such commerce is clearly excessive in relation to the putative local benefits," considering whether the interest could be promoted as well with a lesser impact. Requiring business operations to be performed in the home State is "virtually per se illegal."</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>• Rejected the claim that only intrastate packing was regulated: the order requires an out-of-state operation to be performed in-state
 • Protecting growers' reputation is "surely legitimate," but here Arizona wanted a superior product to bear its name to benefit other growers
@@ -4220,47 +5063,47 @@
 • Toomer v. Witsell: if a State cannot require in-state work to promote employment, it cannot do so to enhance reputation</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
+      <c r="I97" s="2" t="inlineStr">
         <is>
           <t>Source of the balancing tier for evenhanded laws; pair with Brown-Forman's two tiers and the CRS sidebar, and note that its in-state processing rule reappears in South-Central Timber.</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="n">
+    <row r="98">
+      <c r="A98" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
         <is>
           <t>Maine v. Taylor (1986)</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Dormant Commerce Clause: discrimination</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Taylor, a Maine bait dealer, imported 158,000 live golden shiners despite Maine's ban on importing live baitfish and was indicted under the federal Lacey Act. He argued that the Maine ban violated the Commerce Clause.</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Maine's ban is valid because it serves legitimate local purposes (keeping out parasites and nonnative species) that could not adequately be served by available nondiscriminatory alternatives.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>A law that discriminates on its face or in practical effect survives only if the State shows a legitimate local purpose that cannot be served as well by available nondiscriminatory means (Hughes v. Oklahoma); Tennessee Wine (2019) describes this as requiring narrow tailoring. Laws that burden commerce only incidentally get Pike balancing.</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>• An "abstract possibility" of developing tests is not an available alternative; a State need not "develop new and unproven means of protection at an uncertain cost"
 • The Lacey Act did not authorize the ban or lower scrutiny; congressional consent must be "unmistakably clear" (South-Central Timber)
@@ -4268,47 +5111,47 @@
 • Stevens dissent ("something fishy"): ambiguity about dangers and alternatives should defeat, not sustain, a discriminatory law (quoting Dean Milk)</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr">
+      <c r="I98" s="2" t="inlineStr">
         <is>
           <t>The rare discriminatory law that survives; contrast Dean Milk and Philadelphia v. New Jersey, and use "does not elevate free trade above all other values" for the State's side.</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="n">
+    <row r="99">
+      <c r="A99" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
         <is>
           <t>Reeves, Inc. v. Stake (1980)</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Market participant exception</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>During a cement shortage, South Dakota's state-owned cement plant supplied all South Dakota customers first. Reeves, a Wyoming ready-mix company that bought about 95% of its cement there, had to cut production 76%.</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>The resident preference is valid because South Dakota acted as a market participant, not a market regulator.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>Market participant exception: absent congressional action, a State participating in the market may favor its own citizens (Alexandria Scrap). The Commerce Clause responds principally to state taxes and regulation, not to States acting as traders.</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>• Reasons: state sovereignty, a trader's right to choose its customers, evenhandedness with private sellers, and Congress is better suited to these questions
 • Cement is not a natural resource; South Dakota did not restrict access to limestone or bar private plants
@@ -4316,47 +5159,47 @@
 • Powell dissent: the State may meet its own public needs but may not withhold cement from interstate commerce to benefit private in-state businesses</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
+      <c r="I99" s="2" t="inlineStr">
         <is>
           <t>Anchor case for the market participant exception; show its limits with South-Central Timber (downstream conditions) and Camps Newfound (an open-ended tax exemption is not analogous).</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="n">
+    <row r="100">
+      <c r="A100" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t>South-Central Timber Dev., Inc. v. Wunnicke (1984)</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Market participant; congressional consent</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Alaska sold state timber at a reduced price on condition that buyers process it in Alaska ("primary manufacture") before shipping it out. South-Central, which shipped unprocessed logs almost entirely to Japan, sued.</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Federal policy for federal timber did not authorize Alaska's rule, and (plurality) Alaska was not shielded as a market participant, so the requirement fell as a virtually per se invalid restraint on export of unprocessed logs.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>Congressional authorization of state burdens on commerce must be "unmistakably clear"; a parallel federal policy is not enough. Plurality: a State may burden commerce within the market in which it participates, but may not impose conditions with a substantial regulatory effect in a downstream market.</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>• Three elements absent in Reeves: foreign commerce, a natural resource, and restrictions on resale
 • Substance over labels: Alaska could not avoid the ruling by keeping title until processing ended
@@ -4364,94 +5207,94 @@
 • Rehnquist dissent: the line is "artificial"; Alaska is just paying buyers to process in-state, which it could do by selling only to in-state processors, subsidizing, or processing itself</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr">
         <is>
           <t>Marks the outer limit of Reeves and states the clear-statement rule for congressional consent (applied again in Maine v. Taylor); Brennan's concurrence and Rehnquist's dissent both question the doctrine's coherence.</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="n">
+    <row r="101">
+      <c r="A101" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
         <is>
           <t>Brown-Forman Distillers v. N.Y. State Liquor Authority (1986)</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Dormant Commerce Clause framework</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>The reading excerpts only the Court's statement of doctrine; it gives no facts.</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>The excerpt omits the disposition; it is assigned for its two-tiered framework.</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>Two-tiered approach: a law that directly regulates or discriminates against interstate commerce, or favors in-state over out-of-state interests, is generally struck down without further inquiry; a law with only indirect effects that regulates evenhandedly is upheld unless the burden clearly exceeds the local benefits (Pike).</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>• A statute that by its terms favors in-state producers falls in the tier struck down without further inquiry
 • No clear line separates the virtually per se invalid tier from Pike balancing
 • In either tier "the critical consideration is the overall effect of the statute on both local and interstate activity"</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
+      <c r="I101" s="2" t="inlineStr">
         <is>
           <t>Use as the organizing framework for any dormant Commerce Clause answer: classify the law as discriminatory (Dean Milk, Maine v. Taylor) or evenhanded (Pike), then apply the matching test.</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="4" t="n">
+    <row r="102">
+      <c r="A102" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="B102" s="4" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="C84" s="5" t="inlineStr">
+      <c r="C102" s="5" t="inlineStr">
         <is>
           <t>Bank of the United States Debate (1791)</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr">
+      <c r="D102" s="4" t="inlineStr">
         <is>
           <t>Implied powers; strict construction</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
+      <c r="E102" s="4" t="inlineStr">
         <is>
           <t>In the House debate on chartering the first Bank of the United States, Madison argued the bill was unconstitutional and Fisher Ames answered him.</t>
         </is>
       </c>
-      <c r="F84" s="4" t="inlineStr">
+      <c r="F102" s="4" t="inlineStr">
         <is>
           <t>No judicial holding; the House passed the bank bill over Madison's objection.</t>
         </is>
       </c>
-      <c r="G84" s="4" t="inlineStr">
+      <c r="G102" s="4" t="inlineStr">
         <is>
           <t>Madison: the federal government holds only particular granted powers; the Necessary and Proper Clause is "merely declaratory" and limited to "means necessary to the end, and incident to the nature of the specified powers," and a bank was at most "convenient." Ames: government is "the highest kind of corporation" with tacit powers needed for its ends, unless repugnant to natural rights, expressly reserved rights, or powers assigned to the States.</t>
         </is>
       </c>
-      <c r="H84" s="4" t="inlineStr">
+      <c r="H102" s="4" t="inlineStr">
         <is>
           <t>• Madison's only possible sources: taxing for the general welfare, borrowing, and Necessary and Proper (NOT the commerce power); "It does not borrow a shilling"
 • Madison's "chain": borrowing to capital, capital to a bank, a bank to a charter; such a chain "will reach every object of legislation"
@@ -4459,141 +5302,141 @@
 • Ames: Congress already taxed ships and erected lighthouses as incidents of regulating trade; implied power's danger is uncertainty, and strict rules "only set up one construction against another"</t>
         </is>
       </c>
-      <c r="I84" s="4" t="inlineStr">
+      <c r="I102" s="4" t="inlineStr">
         <is>
           <t>Frames the strict versus broad construction debate that McCulloch resolved; ask whether Madison's 1791 position squares with Federalist No. 44 and his 1815 openness to a bank.</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="4" t="n">
+    <row r="103">
+      <c r="A103" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B85" s="4" t="inlineStr">
+      <c r="B103" s="4" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr">
+      <c r="C103" s="5" t="inlineStr">
         <is>
           <t>Fisher Ames Letters (1791)</t>
         </is>
       </c>
-      <c r="D85" s="4" t="inlineStr">
+      <c r="D103" s="4" t="inlineStr">
         <is>
           <t>Bank debate politics</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
+      <c r="E103" s="4" t="inlineStr">
         <is>
           <t>Private letters from Ames to Thomas Dwight and George Richards Minot reporting on the House bank debate.</t>
         </is>
       </c>
-      <c r="F85" s="4" t="inlineStr">
+      <c r="F103" s="4" t="inlineStr">
         <is>
           <t>No holding; Ames reported that the bill passed easily, "a strong proof of the little impression" Madison's attack made.</t>
         </is>
       </c>
-      <c r="G85" s="4" t="inlineStr">
+      <c r="G103" s="4" t="inlineStr">
         <is>
           <t>Shows Federalists dismissed Madison's constitutional objection and that the bill's real political difficulty was its effect on moving the capital from Philadelphia to the Potomac.</t>
         </is>
       </c>
-      <c r="H85" s="4" t="inlineStr">
+      <c r="H103" s="4" t="inlineStr">
         <is>
           <t>• Ames called Madison's speech "full of casuistry and sophistry"
 • Madison read at length from state ratification debates to argue for strict construction
 • "Great point of difficulty": the bank might leave Congress "fast anchored and immovable" in Philadelphia</t>
         </is>
       </c>
-      <c r="I85" s="4" t="inlineStr">
+      <c r="I103" s="4" t="inlineStr">
         <is>
           <t>Use with McCulloch's reliance on practice to show the bank question was settled politically before it reached the Court.</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="4" t="n">
+    <row r="104">
+      <c r="A104" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B86" s="4" t="inlineStr">
+      <c r="B104" s="4" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
+      <c r="C104" s="5" t="inlineStr">
         <is>
           <t>The Federalist No. 11 (1787)</t>
         </is>
       </c>
-      <c r="D86" s="4" t="inlineStr">
+      <c r="D104" s="4" t="inlineStr">
         <is>
           <t>National commerce rationale</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
+      <c r="E104" s="4" t="inlineStr">
         <is>
           <t>Hamilton's essay to the people of New York on the Union's commercial benefits.</t>
         </is>
       </c>
-      <c r="F86" s="4" t="inlineStr">
+      <c r="F104" s="4" t="inlineStr">
         <is>
           <t>No holding; argues that commercial unity requires a unified government.</t>
         </is>
       </c>
-      <c r="G86" s="4" t="inlineStr">
+      <c r="G104" s="4" t="inlineStr">
         <is>
           <t>"An unrestrained intercourse between the States" advances each State's trade, and "an unity of commercial, as well as political interests, can only result from an unity of government."</t>
         </is>
       </c>
-      <c r="H86" s="4" t="inlineStr">
+      <c r="H104" s="4" t="inlineStr">
         <is>
           <t>• Trade among disunited States would be "fettered, interrupted and narrowed by a multiplicity of causes"
 • Interchange lets a State whose staple fails from a bad harvest call on another's
 • Supports the national-market goal that the CRS sidebar says the dormant Commerce Clause preserves</t>
         </is>
       </c>
-      <c r="I86" s="4" t="inlineStr">
+      <c r="I104" s="4" t="inlineStr">
         <is>
           <t>Founding-era support for the national-market purpose behind both the commerce power and the dormant Commerce Clause; pair with Ginsburg's NFIB account of the Commerce Clause as the answer to the Articles' failures.</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="4" t="n">
+    <row r="105">
+      <c r="A105" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="B105" s="4" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
+      <c r="C105" s="5" t="inlineStr">
         <is>
           <t>The Federalist No. 44 (1788)</t>
         </is>
       </c>
-      <c r="D87" s="4" t="inlineStr">
+      <c r="D105" s="4" t="inlineStr">
         <is>
           <t>Necessary and Proper Clause</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
+      <c r="E105" s="4" t="inlineStr">
         <is>
           <t>Madison defends the Necessary and Proper Clause against Anti-Federalist attack.</t>
         </is>
       </c>
-      <c r="F87" s="4" t="inlineStr">
+      <c r="F105" s="4" t="inlineStr">
         <is>
           <t>No holding; argues that "without the substance of this power, the whole constitution would be a dead letter."</t>
         </is>
       </c>
-      <c r="G87" s="4" t="inlineStr">
+      <c r="G105" s="4" t="inlineStr">
         <is>
           <t>Wherever the end is required, the means are authorized; even silence would have yielded the needed powers "by unavoidable implication." Misuse is checked first by the executive and judiciary and, in the last resort, by the people at elections.</t>
         </is>
       </c>
-      <c r="H87" s="4" t="inlineStr">
+      <c r="H105" s="4" t="inlineStr">
         <is>
           <t>• Four rejected alternatives: copy the Articles' "expressly" rule, a positive enumeration, a negative enumeration, or silence (NOT an "absolutely necessary" limit)
 • "Expressly" would be construed either so strictly as to disarm the government or so loosely as to destroy the restriction
@@ -4601,47 +5444,47 @@
 • The reader asks whether Madison's 1791 bank speech is consistent with this essay</t>
         </is>
       </c>
-      <c r="I87" s="4" t="inlineStr">
+      <c r="I105" s="4" t="inlineStr">
         <is>
           <t>Use with McCulloch for the broad view of implied means, and against Madison's own 1791 strict construction to show how his position shifted.</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="4" t="n">
+    <row r="106">
+      <c r="A106" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B88" s="4" t="inlineStr">
+      <c r="B106" s="4" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="C88" s="5" t="inlineStr">
+      <c r="C106" s="5" t="inlineStr">
         <is>
           <t>Brutus No. 1 (1787)</t>
         </is>
       </c>
-      <c r="D88" s="4" t="inlineStr">
+      <c r="D106" s="4" t="inlineStr">
         <is>
           <t>Anti-Federalist critique</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
+      <c r="E106" s="4" t="inlineStr">
         <is>
           <t>Anti-Federalist essay in the New York Journal asking whether the States should be consolidated into one great republic.</t>
         </is>
       </c>
-      <c r="F88" s="4" t="inlineStr">
+      <c r="F106" s="4" t="inlineStr">
         <is>
           <t>No holding; argues the Constitution approaches so near consolidation that it "must, if executed, certainly and infallibly terminate in it."</t>
         </is>
       </c>
-      <c r="G88" s="4" t="inlineStr">
+      <c r="G106" s="4" t="inlineStr">
         <is>
           <t>The Necessary and Proper and Supremacy Clauses make the government "a complete one, and not a confederation"; the clause "may receive a construction to justify the passing almost any law" and could "entirely abolish the State legislatures."</t>
         </is>
       </c>
-      <c r="H88" s="4" t="inlineStr">
+      <c r="H106" s="4" t="inlineStr">
         <is>
           <t>• Objected to the breadth of federal power, not its weakness
 • Example: Congress could repeal a state revenue law as obstructing a federal tax it deems necessary
@@ -4649,47 +5492,47 @@
 • Willett's Bonner concurrence invokes Brutus's fear of expansion by implication</t>
         </is>
       </c>
-      <c r="I88" s="4" t="inlineStr">
+      <c r="I106" s="4" t="inlineStr">
         <is>
           <t>The Anti-Federalist prediction against which to test McCulloch and the modern commerce cases; cite it for the argument that implied powers lead to consolidation.</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="4" t="n">
+    <row r="107">
+      <c r="A107" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B89" s="4" t="inlineStr">
+      <c r="B107" s="4" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C107" s="5" t="inlineStr">
         <is>
           <t>Tenth Amendment Debate, House of Representatives (1789)</t>
         </is>
       </c>
-      <c r="D89" s="4" t="inlineStr">
+      <c r="D107" s="4" t="inlineStr">
         <is>
           <t>Tenth Amendment; implied powers</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
+      <c r="E107" s="4" t="inlineStr">
         <is>
           <t>In August 1789 the House considered the proposition that became the Tenth Amendment; Tucker, and later Gerry, moved to reserve all powers "not expressly delegated."</t>
         </is>
       </c>
-      <c r="F89" s="4" t="inlineStr">
+      <c r="F107" s="4" t="inlineStr">
         <is>
           <t>No holding; the House rejected "expressly" and adopted the text with "or to the people" and "to the United States" added.</t>
         </is>
       </c>
-      <c r="G89" s="4" t="inlineStr">
+      <c r="G107" s="4" t="inlineStr">
         <is>
           <t>The Tenth Amendment reserves powers not delegated, not powers not expressly delegated, so whether a power is delegated depends on fair construction, as McCulloch later held, unlike the Articles of Confederation's "expressly" rule.</t>
         </is>
       </c>
-      <c r="H89" s="4" t="inlineStr">
+      <c r="H107" s="4" t="inlineStr">
         <is>
           <t>• Madison: it is impossible to confine a government to express powers unless the Constitution recounted "every minutiae"
 • Sherman: corporate bodies possess all powers incident to their corporate capacity without express statement
@@ -4697,140 +5540,140 @@
 • Professor's response to King's claim that the Amendment is "a clear delineation" of power: "Is it really this easy?"</t>
         </is>
       </c>
-      <c r="I89" s="4" t="inlineStr">
+      <c r="I107" s="4" t="inlineStr">
         <is>
           <t>Use to rebut any argument that the Tenth Amendment limits Congress to express powers; it links directly to McCulloch's reading of the omitted word.</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="4" t="n">
+    <row r="108">
+      <c r="A108" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B90" s="4" t="inlineStr">
+      <c r="B108" s="4" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr">
+      <c r="C108" s="5" t="inlineStr">
         <is>
           <t>Lighthouses Act (1789)</t>
         </is>
       </c>
-      <c r="D90" s="4" t="inlineStr">
+      <c r="D108" s="4" t="inlineStr">
         <is>
           <t>Early implied powers</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
+      <c r="E108" s="4" t="inlineStr">
         <is>
           <t>The First Congress assumed the cost of lighthouses, beacons, buoys and public piers (after one year only if the State ceded them), funded a new lighthouse near the Chesapeake Bay entrance, and left pilots to state law until Congress acts.</t>
         </is>
       </c>
-      <c r="F90" s="4" t="inlineStr">
+      <c r="F108" s="4" t="inlineStr">
         <is>
           <t>No holding; the reader asks which Article I, § 8 power authorizes it.</t>
         </is>
       </c>
-      <c r="G90" s="4" t="inlineStr">
+      <c r="G108" s="4" t="inlineStr">
         <is>
           <t>Early congressional practice treated such measures as incidents of an enumerated power: Ames in 1791 cited erecting lighthouses as an incident of the power to regulate trade.</t>
         </is>
       </c>
-      <c r="H90" s="4" t="inlineStr">
+      <c r="H108" s="4" t="inlineStr">
         <is>
           <t>• No clause mentions lighthouses; the answer is an incident of the power to regulate commerce (Ames)
 • § 4 left regulation of pilots to existing and future state law until Congress provides otherwise</t>
         </is>
       </c>
-      <c r="I90" s="4" t="inlineStr">
+      <c r="I108" s="4" t="inlineStr">
         <is>
           <t>Evidence that the First Congress read its powers to include unlisted means, supporting the broad view later adopted in McCulloch.</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="4" t="n">
+    <row r="109">
+      <c r="A109" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B91" s="4" t="inlineStr">
+      <c r="B109" s="4" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
+      <c r="C109" s="5" t="inlineStr">
         <is>
           <t>Madison, Seventh Annual Message (1815)</t>
         </is>
       </c>
-      <c r="D91" s="4" t="inlineStr">
+      <c r="D109" s="4" t="inlineStr">
         <is>
           <t>National bank</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
+      <c r="E109" s="4" t="inlineStr">
         <is>
           <t>President Madison's annual message after the War of 1812, addressing a $120 million national debt and the currency.</t>
         </is>
       </c>
-      <c r="F91" s="4" t="inlineStr">
+      <c r="F109" s="4" t="inlineStr">
         <is>
           <t>No holding; urges restoring a uniform national currency and says that if state banks cannot do it, "the probable operation of a national bank will merit consideration."</t>
         </is>
       </c>
-      <c r="G91" s="4" t="inlineStr">
+      <c r="G109" s="4" t="inlineStr">
         <is>
           <t>Shows President Madison open to a national bank he had opposed as unconstitutional as a congressman in 1791, consistent with McCulloch's point that experience led former opponents to support the second bank.</t>
         </is>
       </c>
-      <c r="H91" s="4" t="inlineStr">
+      <c r="H109" s="4" t="inlineStr">
         <is>
           <t>• Both points: restore "the benefits of an uniform national currency," and a national bank merits consideration if state banks fail
 • Fallback: government notes as a medium of circulation
 • He did NOT call a national bank unconstitutional; contrast Congressman Madison in 1791</t>
         </is>
       </c>
-      <c r="I91" s="4" t="inlineStr">
+      <c r="I109" s="4" t="inlineStr">
         <is>
           <t>Use to illustrate constitutional settlement by practice (McCulloch) and the tension in Madison's own views.</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="4" t="n">
+    <row r="110">
+      <c r="A110" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B92" s="4" t="inlineStr">
+      <c r="B110" s="4" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="C92" s="5" t="inlineStr">
+      <c r="C110" s="5" t="inlineStr">
         <is>
           <t>CRS Legal Sidebar on the Dormant Commerce Clause (2023)</t>
         </is>
       </c>
-      <c r="D92" s="4" t="inlineStr">
+      <c r="D110" s="4" t="inlineStr">
         <is>
           <t>Dormant Commerce Clause overview</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
+      <c r="E110" s="4" t="inlineStr">
         <is>
           <t>Congressional Research Service sidebar on a 2023 Supreme Court decision that narrowed the dormant Commerce Clause and upheld a state animal welfare law.</t>
         </is>
       </c>
-      <c r="F92" s="4" t="inlineStr">
+      <c r="F110" s="4" t="inlineStr">
         <is>
           <t>No holding; summarizes the modern doctrine.</t>
         </is>
       </c>
-      <c r="G92" s="4" t="inlineStr">
+      <c r="G110" s="4" t="inlineStr">
         <is>
           <t>Though the Commerce Clause is a grant to Congress, it is read to bar state laws that unduly restrict interstate commerce when Congress is "dormant." Discriminatory laws driven by economic protectionism generally fall unless "narrowly tailored to advance a legitimate local purpose" with no reasonable nondiscriminatory alternative; facially neutral laws that unduly burden commerce get Pike balancing.</t>
         </is>
       </c>
-      <c r="H92" s="4" t="inlineStr">
+      <c r="H110" s="4" t="inlineStr">
         <is>
           <t>• Purpose: it "prevents the States from adopting protectionist measures and thus preserves a national market for goods and services"
 • A neutral, safety-based law with incidental effects is upheld unless the burden is clearly excessive relative to local benefits
@@ -4838,47 +5681,93 @@
 • The case law is "highly fact-specific"</t>
         </is>
       </c>
-      <c r="I92" s="4" t="inlineStr">
+      <c r="I110" s="4" t="inlineStr">
         <is>
           <t>A compact statement of the modern doctrine to open an answer before applying Dean Milk, Pike or Maine v. Taylor.</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="n">
+    <row r="111">
+      <c r="A111" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>CALI Assessment: Contemporary Commerce Clause</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>Commerce Clause: practice</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>A self-test on post-1995 commerce cases.</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>The professor's note asks whether recreational bicycles are instrumentalities of interstate commerce.</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="inlineStr">
+        <is>
+          <t>Ties to the Week 7 vehicle cases: Protho (cars are instrumentalities by class) vs. Chavarria (generic "motor vehicles" are not per se instrumentalities).</t>
+        </is>
+      </c>
+      <c r="H111" s="6" t="inlineStr">
+        <is>
+          <t>• Would the bicycle answer differ in the Tenth Circuit (Chavarria)?
+• Class of object vs. particular use</t>
+        </is>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>Use to show the circuit split on instrumentalities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
         <is>
           <t>Camps Newfound/Owatonna v. Town of Harrison (1997)</t>
         </is>
       </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Dormant Commerce Clause: tax exemptions</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Maine gave charities a full property tax exemption but limited it for charities operated principally for nonresidents. A Christian Science summer camp whose campers were about 95% nonresidents, charging about $400 a week, got no exemption at all.</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Maine's charitable exemption, which excluded charities operated principally for nonresidents, violates the dormant Commerce Clause.</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t>A State may not tax an enterprise more heavily because its customers come from other States, and nonprofits get the same protection; calling a discriminatory tax a real estate tax or a charitable exemption does not escape the dormant Commerce Clause.</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>• A nonprofit camp is "unquestionably engaged in commerce, not only as a purchaser, but also as a provider of goods and services"
 • A real estate tax geared to imported goods would be the "functional equivalent of an import tariff" (West Lynn)
@@ -4886,47 +5775,47 @@
 • Scalia dissent: the doctrine "has drifted far from its moorings"; Thomas dissent: the majority created a "dormant" Necessary and Proper Clause, since land does not move in commerce</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr">
+      <c r="I112" s="2" t="inlineStr">
         <is>
           <t>Extends the discrimination tier to nonprofits and tax exemptions and shows the limits of the market participant exception; the dissents supply the critique of the whole doctrine.</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="n">
+    <row r="113">
+      <c r="A113" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="C94" s="3" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
         <is>
           <t>City of Boerne v. Flores (1997)</t>
         </is>
       </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Section 5 enforcement power</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Boerne, Texas, relying on a historic-preservation ordinance, denied the Archbishop a permit to enlarge St. Peter Catholic Church. The Archbishop sued under RFRA, which Congress passed after Employment Division v. Smith to restore the compelling-interest test against every level of government.</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>RFRA exceeds Congress's power under § 5 of the Fourteenth Amendment as applied to the States because it makes a substantive change in constitutional protections rather than enforcing them.</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>Congruence and proportionality: "There must be a congruence and proportionality between the injury to be prevented or remedied and the means adopted to that end." Section 5 lets Congress remedy and prevent violations, even by barring some constitutional conduct, but not redefine the right: "Congress does not enforce a constitutional right by changing what the right is."</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>• Background: Sherbert required a compelling interest for substantial burdens; Smith held "neutral, generally applicable laws may be applied to religious practices" without one, partly because courts cannot judge a belief's centrality; RFRA restored Sherbert and Yoder by statute and added least restrictive means
 • The thin record was not RFRA's "most serious shortcoming"; its sweep was: every government, all laws past and future, no end date, and "the most demanding test known to constitutional law"
@@ -4934,14 +5823,14 @@
 • The Court interprets the Constitution in cases: "it is this Court's precedent, not RFRA, which must control"; the Civil Rights Cases treat § 5 as corrective, not "general legislation"</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr">
+      <c r="I113" s="2" t="inlineStr">
         <is>
           <t>The central limit on Congress's § 5 power and a judicial-supremacy statement in the Marbury line; counter with Kennedy's concession that Congress has a duty to interpret the Constitution and gets wide latitude in choosing remedies.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I94"/>
+  <autoFilter ref="A1:I113"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4959,37 +5848,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Con Law case chart, Weeks 1-9 (closed universe: your reader and fact banks).</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>One row per case, plus key documents (shaded rows) such as the Federalist Papers and Brutus.</t>
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>One row per case, plus key documents (gray rows) such as the Federalist Papers and Brutus, plus secondary readings (tan rows) such as CRS reports, treatise sections and the Senate legislation page.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Use the filter arrows in the header row to show one Week, one Type (Case or Document), or one Topic.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Where a reader excerpt omits facts or a disposition, the cell says so instead of filling in from outside the reader.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>61 cases and 32 documents.</t>
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>61 cases, 32 documents and 19 secondary readings.</t>
         </is>
       </c>
     </row>

--- a/Con_Law_Case_Chart.xlsx
+++ b/Con_Law_Case_Chart.xlsx
@@ -8691,7 +8691,7 @@
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
-          <t>Affirmed: the complaint fails to state a dormant Commerce Clause claim. The Court unanimously rejects an "almost per se" rule against state laws with extraterritorial effects; a fractured majority rejects the Pike claim.</t>
+          <t>Affirmed (Ninth Circuit): the complaint fails to state a dormant Commerce Clause claim. All nine Justices reject an "almost per se" rule against state laws with extraterritorial effects (Part III: 5-Justice majority, with Roberts, Alito, Kavanaugh and Jackson agreeing). The Pike claim fails on a fractured vote: IV-C's no-substantial-burden reasoning has only 4 votes, and IV-B's incommensurability reasoning only 3.</t>
         </is>
       </c>
       <c r="I149" s="3" t="inlineStr">
@@ -8701,19 +8701,25 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>• Gorsuch for the Court (Parts I-III, IV-A, V): no extraterritoriality rule; Pike's heartland = discrimination
-• Part IV-B (Gorsuch, Thomas, Barrett): courts can't weigh economic costs against moral/health benefits; "incommensurable" ("whether a particular line is longer than a particular rock is heavy"); take it to Congress
-• Part IV-C (Gorsuch, Thomas, Sotomayor, Kagan): no substantial burden pled; Exxon analogy (market share shifts among out-of-state firms; "That goes for pigs no less than gas stations")
-• Sotomayor (with Kagan): Pike survives; courts CAN balance; claim fails only for no substantial burden
-• Barrett: burdens are substantial, but benefits and burdens are incommensurable
-• Roberts (with Alito, Kavanaugh, Jackson), partial dissent: substantial burden pled (market-wide harms, compliance forced even on producers not selling in CA, Edgar's "nationwide reach"); would remand for Pike balancing
-• Kavanaugh: six Justices keep Pike balancing; Prop 12 may also raise Import-Export, Privileges and Immunities and Full Faith and Credit issues; "California knows best"
-• Count: 6 Justices say courts can balance under Pike; the judgment rests on IV-B + IV-C together</t>
+          <t>• VOTE MAP (handout), Gorsuch's lead opinion: I Facts (5: NG/CT/SS/EK/ACB)
+• II No discrimination (5)
+• III No per se extraterritoriality rule (5, + JR/SA/BK/KBJ in agreement = 9)
+• IV-A No clear line between discrimination and Pike cases (5; Roberts seemed to agree that many leading dormant CC cases are really about protectionism)
+• IV-B Incommensurability: courts can't weigh economic costs against moral/health benefits ("whether a particular line is longer than a particular rock is heavy") (3: NG/CT/ACB; 6 disagree: SS/EK + JR/SA/BK/KBJ)
+• IV-C Pike pleading requirement not met: no substantial burden pled; Exxon analogy ("That goes for pigs no less than gas stations") (4: NG/CT/SS/EK; 5 disagree: ACB + JR/SA/BK/KBJ)
+• IV-D Federalism + incommensurability (3: NG/CT/ACB; 6 implicitly disagree)
+• V Judgment affirmed (5)
+• IS THE OPINION FRACTURED? Gorsuch/Thomas/Barrett say no (the dissents "seek to characterize today's decision as 'fractured'"); everyone else says yes
+• IS PIKE OVERRULED? No. Kavanaugh: IV-B and IV-D "would essentially overrule the Pike balancing test," but "six Justices of this Court affirmatively retain" it (SS, EK + JR, SA, BK, KBJ)
+• WHAT'S BINDING? Majority parts: I, II, III, IV-A, V. Gorsuch (IV-D) claims the judgment "depends equally" on IV-B and IV-C; Kavanaugh: IV-B and IV-D "are not controlling precedent," but IV-C (4-Justice plurality applying Pike) is controlling for the judgment on the Pike claim
+• FIVE Justices think a substantial burden WAS pled: Barrett ("The complaint plausibly alleges that Proposition 12's costs are pervasive, burdensome, and will be felt primarily (but not exclusively) outside California"; so she doesn't join IV-C, but votes to affirm on incommensurability) + Roberts/Alito/Kavanaugh/Jackson (would remand for Pike balancing)
+• FEDERALISM CUTS BOTH WAYS: Gorsuch/Thomas/Barrett (IV-D): the dissent's test means "one complaint from an unhappy out-of-state producer and—presto—the Constitution would protect the sale of horsemeat" (also fireworks, plastic bags); Kavanaugh: California "undermines federalism" by forcing other States' farmers to follow its laws
+• Kavanaugh also flags Import-Export, Privileges and Immunities and Full Faith and Credit issues</t>
         </is>
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>Modern statement that the dormant CC is about discrimination. For a facially neutral law, walk the Truesdell questions (face, effect, purpose), then Pike: substantial burden first, then 'clearly excessive' balancing. Shows the Court's caution: leave nationwide policy to Congress under the 'wakeful' Commerce Clause.</t>
+          <t>Modern statement that the dormant CC is about discrimination. For a facially neutral law, walk the Truesdell questions (face, effect, purpose), then Pike: substantial burden first, then 'clearly excessive' balancing. Count votes carefully: Pike balancing survives (6 Justices), the extraterritoriality argument is dead (9), and the binding Pike holding is at most IV-C's narrow pleading point. Argue federalism from both sides (horsemeat vs. California dictating farm practices). The Court leaves nationwide policy to Congress under the 'wakeful' Commerce Clause.</t>
         </is>
       </c>
     </row>
@@ -14882,7 +14888,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>Affirmed: the complaint fails to state a dormant Commerce Clause claim. The Court unanimously rejects an "almost per se" rule against state laws with extraterritorial effects; a fractured majority rejects the Pike claim.</t>
+          <t>Affirmed (Ninth Circuit): the complaint fails to state a dormant Commerce Clause claim. All nine Justices reject an "almost per se" rule against state laws with extraterritorial effects (Part III: 5-Justice majority, with Roberts, Alito, Kavanaugh and Jackson agreeing). The Pike claim fails on a fractured vote: IV-C's no-substantial-burden reasoning has only 4 votes, and IV-B's incommensurability reasoning only 3.</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
@@ -14892,19 +14898,25 @@
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>• Gorsuch for the Court (Parts I-III, IV-A, V): no extraterritoriality rule; Pike's heartland = discrimination
-• Part IV-B (Gorsuch, Thomas, Barrett): courts can't weigh economic costs against moral/health benefits; "incommensurable" ("whether a particular line is longer than a particular rock is heavy"); take it to Congress
-• Part IV-C (Gorsuch, Thomas, Sotomayor, Kagan): no substantial burden pled; Exxon analogy (market share shifts among out-of-state firms; "That goes for pigs no less than gas stations")
-• Sotomayor (with Kagan): Pike survives; courts CAN balance; claim fails only for no substantial burden
-• Barrett: burdens are substantial, but benefits and burdens are incommensurable
-• Roberts (with Alito, Kavanaugh, Jackson), partial dissent: substantial burden pled (market-wide harms, compliance forced even on producers not selling in CA, Edgar's "nationwide reach"); would remand for Pike balancing
-• Kavanaugh: six Justices keep Pike balancing; Prop 12 may also raise Import-Export, Privileges and Immunities and Full Faith and Credit issues; "California knows best"
-• Count: 6 Justices say courts can balance under Pike; the judgment rests on IV-B + IV-C together</t>
+          <t>• VOTE MAP (handout), Gorsuch's lead opinion: I Facts (5: NG/CT/SS/EK/ACB)
+• II No discrimination (5)
+• III No per se extraterritoriality rule (5, + JR/SA/BK/KBJ in agreement = 9)
+• IV-A No clear line between discrimination and Pike cases (5; Roberts seemed to agree that many leading dormant CC cases are really about protectionism)
+• IV-B Incommensurability: courts can't weigh economic costs against moral/health benefits ("whether a particular line is longer than a particular rock is heavy") (3: NG/CT/ACB; 6 disagree: SS/EK + JR/SA/BK/KBJ)
+• IV-C Pike pleading requirement not met: no substantial burden pled; Exxon analogy ("That goes for pigs no less than gas stations") (4: NG/CT/SS/EK; 5 disagree: ACB + JR/SA/BK/KBJ)
+• IV-D Federalism + incommensurability (3: NG/CT/ACB; 6 implicitly disagree)
+• V Judgment affirmed (5)
+• IS THE OPINION FRACTURED? Gorsuch/Thomas/Barrett say no (the dissents "seek to characterize today's decision as 'fractured'"); everyone else says yes
+• IS PIKE OVERRULED? No. Kavanaugh: IV-B and IV-D "would essentially overrule the Pike balancing test," but "six Justices of this Court affirmatively retain" it (SS, EK + JR, SA, BK, KBJ)
+• WHAT'S BINDING? Majority parts: I, II, III, IV-A, V. Gorsuch (IV-D) claims the judgment "depends equally" on IV-B and IV-C; Kavanaugh: IV-B and IV-D "are not controlling precedent," but IV-C (4-Justice plurality applying Pike) is controlling for the judgment on the Pike claim
+• FIVE Justices think a substantial burden WAS pled: Barrett ("The complaint plausibly alleges that Proposition 12's costs are pervasive, burdensome, and will be felt primarily (but not exclusively) outside California"; so she doesn't join IV-C, but votes to affirm on incommensurability) + Roberts/Alito/Kavanaugh/Jackson (would remand for Pike balancing)
+• FEDERALISM CUTS BOTH WAYS: Gorsuch/Thomas/Barrett (IV-D): the dissent's test means "one complaint from an unhappy out-of-state producer and—presto—the Constitution would protect the sale of horsemeat" (also fireworks, plastic bags); Kavanaugh: California "undermines federalism" by forcing other States' farmers to follow its laws
+• Kavanaugh also flags Import-Export, Privileges and Immunities and Full Faith and Credit issues</t>
         </is>
       </c>
       <c r="I116" s="3" t="inlineStr">
         <is>
-          <t>Modern statement that the dormant CC is about discrimination. For a facially neutral law, walk the Truesdell questions (face, effect, purpose), then Pike: substantial burden first, then 'clearly excessive' balancing. Shows the Court's caution: leave nationwide policy to Congress under the 'wakeful' Commerce Clause.</t>
+          <t>Modern statement that the dormant CC is about discrimination. For a facially neutral law, walk the Truesdell questions (face, effect, purpose), then Pike: substantial burden first, then 'clearly excessive' balancing. Count votes carefully: Pike balancing survives (6 Justices), the extraterritoriality argument is dead (9), and the binding Pike holding is at most IV-C's narrow pleading point. Argue federalism from both sides (horsemeat vs. California dictating farm practices). The Court leaves nationwide policy to Congress under the 'wakeful' Commerce Clause.</t>
         </is>
       </c>
     </row>
